--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS3"/>
+  <dimension ref="A1:BS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,6 +1414,317 @@
       </c>
       <c r="BS3" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>07:45:06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>00:02</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>02:32</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>07:27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>22:24</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>04:05</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>23:38</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>03:19</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>05:32</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>79</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>161</v>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>GGD</t>
+        </is>
+      </c>
+      <c r="BN4" t="n">
+        <v>97</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1007</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>52.16</v>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS4" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -1427,7 +1738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS3"/>
+  <dimension ref="A1:BS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2407,6 +2718,317 @@
       </c>
       <c r="BS3" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>07:45:08</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>00:18</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>22:28</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>02:41</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>05:52</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>22:39</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>23:52</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>71</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>274</v>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1006</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS4" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -2420,7 +3042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS3"/>
+  <dimension ref="A1:BS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3399,6 +4021,317 @@
         </is>
       </c>
       <c r="BS3" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>07:45:06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>00:21</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>22:32</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>02:42</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>05:51</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>72</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>03:29</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>05:35</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>71</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>356</v>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1007</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>52.16</v>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS4" t="n">
         <v>804</v>
       </c>
     </row>
@@ -3413,7 +4346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS3"/>
+  <dimension ref="A1:BS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4393,6 +5326,317 @@
       </c>
       <c r="BS3" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>07:45:06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>00:12</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>22:22</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>02:39</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>05:52</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>22:33</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>04:10</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>23:46</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>03:25</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>62</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ4" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>186</v>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BN4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>9225</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1006</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS4" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -4406,7 +5650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS3"/>
+  <dimension ref="A1:BS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5382,6 +6626,315 @@
       </c>
       <c r="BS3" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>07:45:07</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>00:08</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>22:18</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>02:34</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>05:47</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>22:29</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>04:05</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>23:42</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>03:21</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>05:31</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>87</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>Yuksek</t>
+        </is>
+      </c>
+      <c r="BJ4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="n">
+        <v>270</v>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN4" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1007</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>52.16</v>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS4" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -5395,7 +6948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS3"/>
+  <dimension ref="A1:BS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6375,6 +7928,317 @@
       </c>
       <c r="BS3" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>07:45:07</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>00:27</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>22:38</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>02:47</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>06:57</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>05:56</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>72</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>22:48</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>04:16</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>03:34</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>05:40</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>75</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>359</v>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1008</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS4" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -6388,7 +8252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS3"/>
+  <dimension ref="A1:BS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7368,6 +9232,317 @@
       </c>
       <c r="BS3" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>07:45:07</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>00:18</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>22:29</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>02:41</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>05:51</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>20:41</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>23:53</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>05:35</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>57</v>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BN4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1006</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS4" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -7381,7 +9556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS3"/>
+  <dimension ref="A1:BS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8357,6 +10532,315 @@
       </c>
       <c r="BS3" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>07:45:07</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>23:34</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>06:13</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>05:10</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>06:48</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>21:57</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>02:46</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>04:55</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>81</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="n">
+        <v>340</v>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1011</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS4" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -8370,7 +10854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS3"/>
+  <dimension ref="A1:BS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9346,6 +11830,317 @@
       </c>
       <c r="BS3" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>07:45:08</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>23:24</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>01:56</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>05:13</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>02:43</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>04:56</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>58</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>187</v>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BN4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1011</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS4" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -9359,7 +12154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS3"/>
+  <dimension ref="A1:BS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10339,6 +13134,317 @@
       </c>
       <c r="BS3" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>07:45:08</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>00:43</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>03:07</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>73</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>23:04</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>04:37</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>00:17</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>03:53</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>84</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>Yuksek</t>
+        </is>
+      </c>
+      <c r="BJ4" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1010</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS4" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS4"/>
+  <dimension ref="A1:BS5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1724,6 +1724,317 @@
         </is>
       </c>
       <c r="BS4" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>11:00:39</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>00:02</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>02:32</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>07:27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>22:24</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>04:05</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>23:38</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>03:19</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>05:32</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>81</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ5" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>129</v>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="BN5" t="n">
+        <v>87</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>5131</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1006</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS5" t="n">
         <v>804</v>
       </c>
     </row>
@@ -1738,7 +2049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS4"/>
+  <dimension ref="A1:BS5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3028,6 +3339,317 @@
         </is>
       </c>
       <c r="BS4" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>11:00:41</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>00:18</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>22:28</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>02:41</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>05:52</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>22:39</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>23:52</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>59</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>271</v>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN5" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1005</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>68.91</v>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS5" t="n">
         <v>804</v>
       </c>
     </row>
@@ -3042,7 +3664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS4"/>
+  <dimension ref="A1:BS5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4332,6 +4954,317 @@
         </is>
       </c>
       <c r="BS4" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>11:00:39</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>00:21</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>22:32</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>02:42</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>05:51</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>72</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>03:29</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>05:35</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>63</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>359</v>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN5" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>6399</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1006</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS5" t="n">
         <v>804</v>
       </c>
     </row>
@@ -4346,7 +5279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS4"/>
+  <dimension ref="A1:BS5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5637,6 +6570,317 @@
       </c>
       <c r="BS4" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>11:00:40</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>00:12</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>22:22</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>02:39</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>05:52</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>22:33</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>04:10</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>23:46</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>03:25</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>69</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ5" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>162</v>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>GGD</t>
+        </is>
+      </c>
+      <c r="BN5" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1006</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>Hafif yağmur</t>
+        </is>
+      </c>
+      <c r="BS5" t="n">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -5650,7 +6894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS4"/>
+  <dimension ref="A1:BS5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6934,6 +8178,315 @@
         </is>
       </c>
       <c r="BS4" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>11:00:40</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>00:08</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>22:18</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>02:34</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>05:47</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>22:29</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>04:05</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>23:42</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>03:21</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>05:31</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>67</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ5" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="n">
+        <v>260</v>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN5" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1005</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>68.91</v>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS5" t="n">
         <v>803</v>
       </c>
     </row>
@@ -6948,7 +8501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS4"/>
+  <dimension ref="A1:BS5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8238,6 +9791,317 @@
         </is>
       </c>
       <c r="BS4" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>11:00:40</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>00:27</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>22:38</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>02:47</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>06:57</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>05:56</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>72</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>22:48</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>04:16</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>03:34</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>05:40</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>66</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ5" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>351</v>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN5" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1007</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>52.16</v>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS5" t="n">
         <v>804</v>
       </c>
     </row>
@@ -8252,7 +10116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS4"/>
+  <dimension ref="A1:BS5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9542,6 +11406,317 @@
         </is>
       </c>
       <c r="BS4" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>11:00:40</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>00:18</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>22:29</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>02:41</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>05:51</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>20:41</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>23:53</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>05:35</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>16.36</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>63</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>46</v>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN5" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1005</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>68.91</v>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS5" t="n">
         <v>804</v>
       </c>
     </row>
@@ -9556,7 +11731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS4"/>
+  <dimension ref="A1:BS5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10841,6 +13016,317 @@
       </c>
       <c r="BS4" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>11:00:41</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>23:34</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>06:13</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>05:10</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>06:48</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>21:57</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>02:46</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>04:55</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>51</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>296</v>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>KBB</t>
+        </is>
+      </c>
+      <c r="BN5" t="n">
+        <v>91</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1008</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS5" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -10854,7 +13340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS4"/>
+  <dimension ref="A1:BS5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12141,6 +14627,317 @@
       </c>
       <c r="BS4" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>11:00:41</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>23:24</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>01:56</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>05:13</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>02:43</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>04:56</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>51</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>207</v>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN5" t="n">
+        <v>62</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1011</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS5" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -12154,7 +14951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS4"/>
+  <dimension ref="A1:BS5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13444,6 +16241,317 @@
         </is>
       </c>
       <c r="BS4" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>11:00:41</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>00:43</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>03:07</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>73</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>23:04</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>04:37</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>00:17</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>03:53</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>58</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ5" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN5" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1011</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS5" t="n">
         <v>804</v>
       </c>
     </row>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS5"/>
+  <dimension ref="A1:BS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2036,6 +2036,317 @@
       </c>
       <c r="BS5" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13:41:45</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>00:02</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>02:32</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>07:27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>22:24</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>04:05</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>23:38</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>03:19</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>05:32</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>85</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>Yuksek</t>
+        </is>
+      </c>
+      <c r="BJ6" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>267</v>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN6" t="n">
+        <v>95</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>2696</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1005</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>68.91</v>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>Hafif yağmur</t>
+        </is>
+      </c>
+      <c r="BS6" t="n">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS5"/>
+  <dimension ref="A1:BS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3650,6 +3961,317 @@
         </is>
       </c>
       <c r="BS5" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13:41:46</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>00:18</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>22:28</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>02:41</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>05:52</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>22:39</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>23:52</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>16.47</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>48</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>247</v>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN6" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1004</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS6" t="n">
         <v>804</v>
       </c>
     </row>
@@ -3664,7 +4286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS5"/>
+  <dimension ref="A1:BS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5265,6 +5887,317 @@
         </is>
       </c>
       <c r="BS5" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13:41:45</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>00:21</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>22:32</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>02:42</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>05:51</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>03:29</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>05:35</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>63</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ6" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>346</v>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN6" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1006</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS6" t="n">
         <v>804</v>
       </c>
     </row>
@@ -5279,7 +6212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS5"/>
+  <dimension ref="A1:BS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6881,6 +7814,317 @@
       </c>
       <c r="BS5" t="n">
         <v>500</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13:41:45</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>00:12</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>22:22</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>02:39</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>05:52</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>22:33</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>04:10</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>23:46</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>03:25</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>58</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>268</v>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN6" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1004</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS6" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -6894,7 +8138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS5"/>
+  <dimension ref="A1:BS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8488,6 +9732,315 @@
       </c>
       <c r="BS5" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13:41:45</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>00:08</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>22:18</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>02:34</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>05:47</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>22:29</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>04:05</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>23:42</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>03:21</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>05:31</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>77</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="n">
+        <v>210</v>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN6" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1003</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>85.69</v>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>Kısa süreli hafif yoğunluklu yağmur</t>
+        </is>
+      </c>
+      <c r="BS6" t="n">
+        <v>520</v>
       </c>
     </row>
   </sheetData>
@@ -8501,7 +10054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS5"/>
+  <dimension ref="A1:BS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10102,6 +11655,317 @@
         </is>
       </c>
       <c r="BS5" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13:41:45</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>00:27</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>22:38</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>02:47</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>06:57</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>05:56</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>22:48</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>04:16</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>03:34</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>05:40</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>62</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ6" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>357</v>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN6" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1007</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>52.16</v>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS6" t="n">
         <v>804</v>
       </c>
     </row>
@@ -10116,7 +11980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS5"/>
+  <dimension ref="A1:BS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11717,6 +13581,317 @@
         </is>
       </c>
       <c r="BS5" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13:41:46</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>00:18</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>22:29</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>02:41</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>05:51</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>20:41</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>73</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>23:53</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>05:35</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ6" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>339</v>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN6" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1004</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS6" t="n">
         <v>804</v>
       </c>
     </row>
@@ -11731,7 +13906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS5"/>
+  <dimension ref="A1:BS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13327,6 +15502,311 @@
       </c>
       <c r="BS5" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13:41:46</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>23:34</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>06:13</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>05:10</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>06:48</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>21:57</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>02:46</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>04:55</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>47</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1006</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS6" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -13340,7 +15820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS5"/>
+  <dimension ref="A1:BS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14937,6 +17417,315 @@
         </is>
       </c>
       <c r="BS5" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13:41:46</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>23:24</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>01:56</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>05:13</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>02:43</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>04:56</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>44</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="n">
+        <v>190</v>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BN6" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1010</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS6" t="n">
         <v>803</v>
       </c>
     </row>
@@ -14951,7 +17740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS5"/>
+  <dimension ref="A1:BS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16553,6 +19342,317 @@
       </c>
       <c r="BS5" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13:41:46</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>00:43</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>03:07</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>23:04</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>04:37</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>00:17</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>03:53</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>22.69</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>22.69</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>22.69</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>59</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ6" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>341</v>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN6" t="n">
+        <v>61</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1011</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS6" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS6"/>
+  <dimension ref="A1:BS7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2347,6 +2347,317 @@
       </c>
       <c r="BS6" t="n">
         <v>500</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15:36:27</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>00:02</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>02:32</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>07:27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>22:24</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>04:05</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>23:38</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>03:19</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>05:32</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>76</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>163</v>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>GGD</t>
+        </is>
+      </c>
+      <c r="BN7" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1005</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>68.91</v>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS7" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -2360,7 +2671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS6"/>
+  <dimension ref="A1:BS7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4273,6 +4584,317 @@
       </c>
       <c r="BS6" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15:36:28</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>00:18</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>22:28</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>02:41</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>05:52</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>22:39</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>23:52</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>81</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>264</v>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN7" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1005</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>68.91</v>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>Hafif yağmur</t>
+        </is>
+      </c>
+      <c r="BS7" t="n">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -4286,7 +4908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS6"/>
+  <dimension ref="A1:BS7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6199,6 +6821,317 @@
       </c>
       <c r="BS6" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15:36:27</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>00:21</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>22:32</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>02:42</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>05:51</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>03:29</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>05:35</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>66</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ7" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>353</v>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN7" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1006</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>Hafif yağmur</t>
+        </is>
+      </c>
+      <c r="BS7" t="n">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -6212,7 +7145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS6"/>
+  <dimension ref="A1:BS7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8125,6 +9058,317 @@
       </c>
       <c r="BS6" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15:36:27</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>00:12</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>22:22</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>02:39</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>05:52</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>22:33</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>04:10</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>23:46</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>03:25</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>54</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>324</v>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN7" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1004</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>Hafif yağmur</t>
+        </is>
+      </c>
+      <c r="BS7" t="n">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -8138,7 +9382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS6"/>
+  <dimension ref="A1:BS7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10041,6 +11285,315 @@
       </c>
       <c r="BS6" t="n">
         <v>520</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15:36:27</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>00:08</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>22:18</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>02:34</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>05:47</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>22:29</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>04:05</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>23:42</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>03:21</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>05:31</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>77</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ7" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="n">
+        <v>190</v>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BN7" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1004</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS7" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -10054,7 +11607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS6"/>
+  <dimension ref="A1:BS7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11966,6 +13519,317 @@
         </is>
       </c>
       <c r="BS6" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15:36:27</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>00:27</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>22:38</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>02:47</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>06:57</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>05:56</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>22:48</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>04:16</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>03:34</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>05:40</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>68</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ7" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>348</v>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN7" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1007</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>52.16</v>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS7" t="n">
         <v>804</v>
       </c>
     </row>
@@ -11980,7 +13844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS6"/>
+  <dimension ref="A1:BS7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13893,6 +15757,317 @@
       </c>
       <c r="BS6" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15:36:27</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>00:18</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>22:29</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>02:41</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>05:51</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>20:41</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>73</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>23:53</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>05:35</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>82</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>Yuksek</t>
+        </is>
+      </c>
+      <c r="BJ7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>353</v>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN7" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1005</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>68.91</v>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>Hafif yağmur</t>
+        </is>
+      </c>
+      <c r="BS7" t="n">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -13906,7 +16081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS6"/>
+  <dimension ref="A1:BS7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15806,6 +17981,315 @@
         </is>
       </c>
       <c r="BS6" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15:36:28</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>23:34</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>06:13</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>05:10</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>06:48</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>21:57</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>02:46</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>04:55</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>48</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ7" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="n">
+        <v>230</v>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="BN7" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1006</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS7" t="n">
         <v>803</v>
       </c>
     </row>
@@ -15820,7 +18304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS6"/>
+  <dimension ref="A1:BS7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17726,6 +20210,315 @@
         </is>
       </c>
       <c r="BS6" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15:36:28</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>23:24</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>01:56</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>05:13</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>02:43</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>04:56</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>41</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ7" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="n">
+        <v>220</v>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="BN7" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1010</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS7" t="n">
         <v>803</v>
       </c>
     </row>
@@ -17740,7 +20533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS6"/>
+  <dimension ref="A1:BS7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19653,6 +22446,317 @@
       </c>
       <c r="BS6" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15:36:28</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>00:43</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>03:07</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>23:04</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>04:37</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>00:17</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>03:53</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>74</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ7" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>349</v>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN7" t="n">
+        <v>97</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1011</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS7" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS7"/>
+  <dimension ref="A1:BS8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2657,6 +2657,317 @@
         </is>
       </c>
       <c r="BS7" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>08:59:06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>00:41</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>02:28</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>06:49</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>05:52</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>22:25</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>04:03</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>23:34</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>03:16</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>05:28</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>87</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>Yuksek</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>315</v>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN8" t="n">
+        <v>99</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>8751</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1010</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS8" t="n">
         <v>804</v>
       </c>
     </row>
@@ -2671,7 +2982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS7"/>
+  <dimension ref="A1:BS8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4895,6 +5206,317 @@
       </c>
       <c r="BS7" t="n">
         <v>500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>08:59:10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>00:55</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>22:25</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>05:55</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>04:09</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>23:49</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>03:24</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>05:32</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>80</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>326</v>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN8" t="n">
+        <v>86</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1010</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS8" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -4908,7 +5530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS7"/>
+  <dimension ref="A1:BS8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7132,6 +7754,317 @@
       </c>
       <c r="BS7" t="n">
         <v>500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>08:59:07</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>00:58</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>22:28</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>06:49</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>05:54</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>22:44</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>04:09</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>23:52</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>03:25</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>05:31</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>73</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>336</v>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN8" t="n">
+        <v>99</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1010</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS8" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -7145,7 +8078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS7"/>
+  <dimension ref="A1:BS8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9369,6 +10302,317 @@
       </c>
       <c r="BS7" t="n">
         <v>500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>08:59:07</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>00:50</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>22:18</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>05:56</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>20:41</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>22:34</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>04:08</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>23:43</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>03:22</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>05:32</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>325</v>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN8" t="n">
+        <v>83</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1009</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS8" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -9382,7 +10626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS7"/>
+  <dimension ref="A1:BS8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11593,6 +12837,315 @@
         </is>
       </c>
       <c r="BS7" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>08:59:08</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>00:45</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>22:14</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>06:47</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>05:50</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>04:03</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>23:39</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>03:17</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>05:27</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>19:54</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>93</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>Yuksek</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="n">
+        <v>270</v>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN8" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1010</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS8" t="n">
         <v>803</v>
       </c>
     </row>
@@ -11607,7 +13160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS7"/>
+  <dimension ref="A1:BS8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13830,6 +15383,317 @@
         </is>
       </c>
       <c r="BS7" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>08:59:08</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>01:03</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>22:34</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>02:43</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>05:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>22:49</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>04:14</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>23:57</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>86</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>Yuksek</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>306</v>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1011</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS8" t="n">
         <v>804</v>
       </c>
     </row>
@@ -13844,7 +15708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS7"/>
+  <dimension ref="A1:BS8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16068,6 +17932,317 @@
       </c>
       <c r="BS7" t="n">
         <v>500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>08:59:09</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>00:55</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>22:25</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>06:49</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>05:54</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>20:48</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>73</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>04:09</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>23:49</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>03:24</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>05:32</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>75</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>303</v>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>KBB</t>
+        </is>
+      </c>
+      <c r="BN8" t="n">
+        <v>88</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1010</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS8" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -16081,7 +18256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS7"/>
+  <dimension ref="A1:BS8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18291,6 +20466,317 @@
       </c>
       <c r="BS7" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>08:59:09</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>36</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>00:12</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>21:42</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>01:56</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>06:09</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>05:14</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>06:49</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>23:07</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>02:43</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>04:51</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>77</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>67</v>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BN8" t="n">
+        <v>86</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1010</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS8" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -18304,7 +20790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS7"/>
+  <dimension ref="A1:BS8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20519,6 +23005,315 @@
         </is>
       </c>
       <c r="BS7" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>08:59:10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>00:03</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>01:52</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>06:14</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>05:16</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>21:47</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>03:26</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>22:57</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>02:39</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>04:52</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>81</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="n">
+        <v>300</v>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>KBB</t>
+        </is>
+      </c>
+      <c r="BN8" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>9000</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS8" t="n">
         <v>803</v>
       </c>
     </row>
@@ -20533,7 +23328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS7"/>
+  <dimension ref="A1:BS8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22757,6 +25552,317 @@
       </c>
       <c r="BS7" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>08:59:10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>01:20</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>22:49</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>03:03</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>07:17</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>21:12</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>23:05</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>04:35</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>00:14</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>03:50</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>05:59</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>18</v>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN8" t="n">
+        <v>80</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS8" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS8"/>
+  <dimension ref="A1:BS9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2969,6 +2969,317 @@
       </c>
       <c r="BS8" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10:00:09</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>70</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>01:12</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>22:04</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>02:25</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>05:55</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>20:39</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>22:26</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>04:01</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>23:31</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>03:12</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>05:25</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>19:46</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>64</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>253</v>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS9" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -2982,7 +3293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS8"/>
+  <dimension ref="A1:BS9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5517,6 +5828,317 @@
       </c>
       <c r="BS8" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10:00:11</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>01:25</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>02:33</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>06:46</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>05:58</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>22:42</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>04:07</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>23:46</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>03:20</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>05:28</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>68</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>174</v>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BN9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS9" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -5530,7 +6152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS8"/>
+  <dimension ref="A1:BS9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8065,6 +8687,317 @@
       </c>
       <c r="BS8" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10:00:10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>01:27</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>22:24</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>05:57</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>20:58</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>73</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>04:07</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>23:49</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>03:21</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>52</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>05:28</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>64</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>167</v>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>GGD</t>
+        </is>
+      </c>
+      <c r="BN9" t="n">
+        <v>17</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS9" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -8078,7 +9011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS8"/>
+  <dimension ref="A1:BS9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10613,6 +11546,317 @@
       </c>
       <c r="BS8" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10:00:10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>01:20</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>22:14</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>02:31</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>06:48</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>05:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>20:48</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>22:36</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>04:06</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>03:18</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>05:29</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>68</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>201</v>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS9" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -10626,7 +11870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS8"/>
+  <dimension ref="A1:BS9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13146,6 +14390,311 @@
         </is>
       </c>
       <c r="BS8" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10:00:10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>01:16</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>22:10</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>02:26</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>05:54</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>20:44</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>22:32</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>04:01</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>23:36</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>73</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>03:13</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>05:23</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS9" t="n">
         <v>803</v>
       </c>
     </row>
@@ -13160,7 +14709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS8"/>
+  <dimension ref="A1:BS9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15695,6 +17244,317 @@
       </c>
       <c r="BS8" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10:00:10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>53</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>01:32</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>02:40</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>06:49</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>22:51</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>04:12</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>23:54</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>03:26</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>52</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>05:32</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>114</v>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="BN9" t="n">
+        <v>50</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS9" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -15708,7 +17568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS8"/>
+  <dimension ref="A1:BS9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18243,6 +20103,317 @@
       </c>
       <c r="BS8" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10:00:11</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>01:25</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>02:33</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>06:46</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>05:57</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>04:07</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>23:46</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>03:20</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>05:28</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>68</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>158</v>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>GGD</t>
+        </is>
+      </c>
+      <c r="BN9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS9" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -18256,7 +20427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS8"/>
+  <dimension ref="A1:BS9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20777,6 +22948,317 @@
       </c>
       <c r="BS8" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10:00:11</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>00:42</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>21:38</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>01:52</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>05:17</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>03:26</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>62</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>23:04</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>02:39</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>04:47</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>66</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>270</v>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS9" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -20790,7 +23272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS8"/>
+  <dimension ref="A1:BS9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23314,6 +25796,317 @@
         </is>
       </c>
       <c r="BS8" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10:00:11</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>00:34</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>01:48</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>05:19</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>21:49</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>03:25</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>22:54</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>04:49</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ9" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>199</v>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN9" t="n">
+        <v>69</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS9" t="n">
         <v>803</v>
       </c>
     </row>
@@ -23328,7 +26121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS8"/>
+  <dimension ref="A1:BS9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25863,6 +28656,317 @@
       </c>
       <c r="BS8" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10:00:11</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>01:50</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>02:59</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>07:13</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>21:19</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>74</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>23:07</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>04:33</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>00:10</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>03:46</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>53</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>05:55</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>67</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>25</v>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN9" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS9" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS9"/>
+  <dimension ref="A1:BS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3280,6 +3280,317 @@
       </c>
       <c r="BS9" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12:22:55</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>62</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>01:39</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>02:21</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>05:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>20:46</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>76</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>22:27</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>03:59</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>23:28</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>03:08</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>05:21</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>19:42</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>52</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>155</v>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>GGD</t>
+        </is>
+      </c>
+      <c r="BN10" t="n">
+        <v>19</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS10" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -3293,7 +3604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS9"/>
+  <dimension ref="A1:BS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6139,6 +6450,317 @@
       </c>
       <c r="BS9" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12:22:56</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>01:50</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>22:17</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>02:29</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>74</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>04:05</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>23:42</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>03:17</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>05:24</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>71</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>263</v>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS10" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -6152,7 +6774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS9"/>
+  <dimension ref="A1:BS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8998,6 +9620,317 @@
       </c>
       <c r="BS9" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12:22:55</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>01:51</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>02:31</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>21:04</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>22:47</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>04:05</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>03:17</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>52</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>05:24</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>66</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>183</v>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BN10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>8865</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>Hafif yağmur</t>
+        </is>
+      </c>
+      <c r="BS10" t="n">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -9011,7 +9944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS9"/>
+  <dimension ref="A1:BS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11857,6 +12790,317 @@
       </c>
       <c r="BS9" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12:22:55</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>01:46</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>22:10</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>02:27</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>22:37</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>04:04</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>23:37</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>03:14</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>05:25</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>57</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ10" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>195</v>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN10" t="n">
+        <v>65</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS10" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -11870,7 +13114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS9"/>
+  <dimension ref="A1:BS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14695,6 +15939,311 @@
         </is>
       </c>
       <c r="BS9" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12:22:55</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>41</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>01:41</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>02:22</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>05:57</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>22:33</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>03:59</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>23:33</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>73</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>03:10</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>05:20</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>19:47</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>59</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS10" t="n">
         <v>803</v>
       </c>
     </row>
@@ -14709,7 +16258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS9"/>
+  <dimension ref="A1:BS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17555,6 +19104,317 @@
       </c>
       <c r="BS9" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12:22:56</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>01:56</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>22:26</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>06:46</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>22:52</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>04:10</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>23:51</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>03:22</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>52</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>05:29</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>353</v>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS10" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -17568,7 +19428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS9"/>
+  <dimension ref="A1:BS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20414,6 +22274,317 @@
       </c>
       <c r="BS9" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12:22:56</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>01:50</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>22:17</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>02:29</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>21:02</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>22:44</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>04:05</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>23:43</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>03:17</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>05:24</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>16.36</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>71</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>265</v>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>9171</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS10" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -20427,7 +22598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS9"/>
+  <dimension ref="A1:BS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23259,6 +25430,315 @@
       </c>
       <c r="BS9" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12:22:56</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>01:07</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>01:48</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>05:20</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>20:19</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>03:23</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>04:43</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>19:14</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ10" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="n">
+        <v>230</v>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="BN10" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS10" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -23272,7 +25752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS9"/>
+  <dimension ref="A1:BS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26107,6 +28587,311 @@
         </is>
       </c>
       <c r="BS9" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12:22:56</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>01:01</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>21:22</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>01:44</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>05:23</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>21:50</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>03:23</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>22:50</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>02:32</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS10" t="n">
         <v>803</v>
       </c>
     </row>
@@ -26121,7 +28906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS9"/>
+  <dimension ref="A1:BS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28967,6 +31752,317 @@
       </c>
       <c r="BS9" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12:22:56</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>02:55</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>07:09</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>06:28</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>23:08</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>04:31</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>00:07</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>03:42</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>53</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>05:51</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>68</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>29</v>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN10" t="n">
+        <v>64</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS10" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS10"/>
+  <dimension ref="A1:BS11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3591,6 +3591,317 @@
       </c>
       <c r="BS10" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>19:24:26</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>19:46</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>01:39</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>02:21</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>05:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>20:46</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>22:27</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>03:59</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>23:28</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>03:08</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>05:21</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>19:42</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>197</v>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN11" t="n">
+        <v>29</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS11" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -3604,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS10"/>
+  <dimension ref="A1:BS11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6761,6 +7072,317 @@
       </c>
       <c r="BS10" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>19:24:27</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>01:50</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>22:17</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>02:29</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>04:05</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>23:42</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>03:17</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>05:24</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>80</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>340</v>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN11" t="n">
+        <v>99</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>Hafif yağmur</t>
+        </is>
+      </c>
+      <c r="BS11" t="n">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -6774,7 +7396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS10"/>
+  <dimension ref="A1:BS11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9931,6 +10553,317 @@
       </c>
       <c r="BS10" t="n">
         <v>500</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>19:24:26</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>01:51</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>02:31</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>21:04</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>22:47</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>04:05</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>03:17</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>52</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>05:24</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>80</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ11" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN11" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS11" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -9944,7 +10877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS10"/>
+  <dimension ref="A1:BS11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13100,6 +14033,317 @@
         </is>
       </c>
       <c r="BS10" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>19:24:26</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>01:46</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>22:10</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>02:27</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>22:37</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>04:04</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>23:37</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>03:14</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>05:25</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>54</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ11" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>312</v>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN11" t="n">
+        <v>74</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS11" t="n">
         <v>803</v>
       </c>
     </row>
@@ -13114,7 +14358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS10"/>
+  <dimension ref="A1:BS11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16244,6 +17488,315 @@
         </is>
       </c>
       <c r="BS10" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>19:24:26</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>01:41</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>02:22</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>05:57</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>22:33</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>03:59</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>23:33</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>73</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>03:10</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>05:20</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>19:47</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ11" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="n">
+        <v>330</v>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN11" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS11" t="n">
         <v>803</v>
       </c>
     </row>
@@ -16258,7 +17811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS10"/>
+  <dimension ref="A1:BS11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19414,6 +20967,317 @@
         </is>
       </c>
       <c r="BS10" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>19:24:27</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>01:56</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>22:26</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>06:46</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>22:52</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>04:10</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>23:51</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>03:22</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>52</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>05:29</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>91</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>Yuksek</t>
+        </is>
+      </c>
+      <c r="BJ11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>348</v>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN11" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>8040</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS11" t="n">
         <v>804</v>
       </c>
     </row>
@@ -19428,7 +21292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS10"/>
+  <dimension ref="A1:BS11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22584,6 +24448,317 @@
         </is>
       </c>
       <c r="BS10" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>19:24:27</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>01:50</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>22:17</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>02:29</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>21:02</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>22:44</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>04:05</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>23:43</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>03:17</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>05:24</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>84</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>Yuksek</t>
+        </is>
+      </c>
+      <c r="BJ11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>317</v>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN11" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS11" t="n">
         <v>804</v>
       </c>
     </row>
@@ -22598,7 +24773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS10"/>
+  <dimension ref="A1:BS11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25738,6 +27913,317 @@
         </is>
       </c>
       <c r="BS10" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>19:24:27</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>44</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>01:07</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>01:48</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>05:20</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>20:19</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>03:23</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>04:43</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>71</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>242</v>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN11" t="n">
+        <v>61</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS11" t="n">
         <v>803</v>
       </c>
     </row>
@@ -25752,7 +28238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS10"/>
+  <dimension ref="A1:BS11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28893,6 +31379,317 @@
       </c>
       <c r="BS10" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>19:24:27</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>01:01</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>21:22</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>01:44</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>05:23</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>21:50</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>03:23</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>22:50</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>02:32</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>67</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>205</v>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN11" t="n">
+        <v>19</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS11" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -28906,7 +31703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS10"/>
+  <dimension ref="A1:BS11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32063,6 +34860,317 @@
       </c>
       <c r="BS10" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>19:24:27</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>02:55</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>07:09</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>06:28</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>23:08</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>04:31</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>00:07</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>03:42</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>53</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>05:51</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>75</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ11" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>29</v>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN11" t="n">
+        <v>94</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS11" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS11"/>
+  <dimension ref="A1:BS12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3902,6 +3902,317 @@
       </c>
       <c r="BS11" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11:36:36</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>19:46</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>02:02</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>21:56</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>02:17</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>06:37</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>22:29</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>03:57</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>23:24</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>03:05</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>05:17</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>250</v>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN12" t="n">
+        <v>95</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS12" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -3915,7 +4226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS11"/>
+  <dimension ref="A1:BS12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7383,6 +7694,317 @@
       </c>
       <c r="BS11" t="n">
         <v>500</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11:36:37</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>02:12</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>22:13</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>02:26</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>06:38</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>22:44</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>04:03</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>23:39</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>03:13</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>05:21</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>64</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ12" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>312</v>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN12" t="n">
+        <v>74</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>9648</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS12" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -7396,7 +8018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS11"/>
+  <dimension ref="A1:BS12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10864,6 +11486,317 @@
       </c>
       <c r="BS11" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11:36:36</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>02:13</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>22:17</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>02:27</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>06:37</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>06:03</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>21:11</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>22:48</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>04:03</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>62</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>23:42</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>03:14</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>05:20</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>62</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ12" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>345</v>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN12" t="n">
+        <v>84</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS12" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -10877,7 +11810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS11"/>
+  <dimension ref="A1:BS12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14345,6 +15278,317 @@
       </c>
       <c r="BS11" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11:36:37</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>02:09</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>02:23</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>22:38</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>04:02</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>23:33</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>03:11</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>05:21</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>19:47</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>61</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>223</v>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="BN12" t="n">
+        <v>99</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS12" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -14358,7 +15602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS11"/>
+  <dimension ref="A1:BS12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17797,6 +19041,315 @@
         </is>
       </c>
       <c r="BS11" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11:36:37</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>02:04</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>02:18</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>06:35</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>20:57</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>22:34</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>03:57</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>23:29</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>73</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>03:06</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>05:16</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>19:43</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>59</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ12" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="n">
+        <v>300</v>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>KBB</t>
+        </is>
+      </c>
+      <c r="BN12" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS12" t="n">
         <v>803</v>
       </c>
     </row>
@@ -17811,7 +19364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS11"/>
+  <dimension ref="A1:BS12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21279,6 +22832,317 @@
       </c>
       <c r="BS11" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11:36:37</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>02:18</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>22:22</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>02:32</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>06:08</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>21:16</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>07:38</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>04:08</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>23:47</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>03:19</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>52</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>05:25</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>78</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ12" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>352</v>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN12" t="n">
+        <v>81</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS12" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -21292,7 +23156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS11"/>
+  <dimension ref="A1:BS12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24760,6 +26624,317 @@
       </c>
       <c r="BS11" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11:36:37</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>02:12</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>22:13</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>02:26</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>06:38</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>06:04</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>04:03</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>23:39</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>03:13</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>05:20</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ12" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>302</v>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>KBB</t>
+        </is>
+      </c>
+      <c r="BN12" t="n">
+        <v>84</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS12" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -24773,7 +26948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS11"/>
+  <dimension ref="A1:BS12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28225,6 +30400,315 @@
       </c>
       <c r="BS11" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11:36:37</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>21:31</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>01:44</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>05:58</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>05:23</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>03:22</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>22:57</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>02:31</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>04:40</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>76</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ12" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN12" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>Gök gürültülü hafif yağmurlu</t>
+        </is>
+      </c>
+      <c r="BS12" t="n">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -28238,7 +30722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS11"/>
+  <dimension ref="A1:BS12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31690,6 +34174,315 @@
       </c>
       <c r="BS11" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11:36:37</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>01:25</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>05:26</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>21:51</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>03:21</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>22:47</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>02:28</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>04:41</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>77</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ12" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="n">
+        <v>120</v>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="BN12" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>7000</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS12" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -31703,7 +34496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS11"/>
+  <dimension ref="A1:BS12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35171,6 +37964,317 @@
       </c>
       <c r="BS11" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11:36:37</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>22:37</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>02:51</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>21:32</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>23:09</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>04:29</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>63</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>00:04</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>03:39</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>05:47</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>69</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ12" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>61</v>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BN12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1019</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS12" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS12"/>
+  <dimension ref="A1:BS13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4213,6 +4213,317 @@
       </c>
       <c r="BS12" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13:19:15</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>02:48</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>21:48</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>02:09</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>06:09</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>21:04</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>77</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>22:31</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>03:53</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>23:18</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>74</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>02:57</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>05:10</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>52</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>341</v>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN13" t="n">
+        <v>16</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS13" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -4226,7 +4537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS12"/>
+  <dimension ref="A1:BS13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8005,6 +8316,317 @@
       </c>
       <c r="BS12" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13:19:16</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>21:19</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>02:55</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>02:18</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>75</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>07:38</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>22:47</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>03:59</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>23:32</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>03:05</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>05:13</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>66</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>185</v>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BN13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS13" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -8018,7 +8640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS12"/>
+  <dimension ref="A1:BS13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11797,6 +12419,317 @@
       </c>
       <c r="BS12" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13:19:15</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>02:55</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>22:09</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>02:19</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>06:29</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>21:23</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>22:50</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>03:59</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>23:36</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>03:06</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>05:13</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>48</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ13" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>358</v>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN13" t="n">
+        <v>31</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1020</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS13" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -11810,7 +12743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS12"/>
+  <dimension ref="A1:BS13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15589,6 +16522,317 @@
       </c>
       <c r="BS12" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13:19:15</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>21:17</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>02:54</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>06:13</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>03:58</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>23:27</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>03:03</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>05:14</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>49</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ13" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>326</v>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1019</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS13" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -15602,7 +16846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS12"/>
+  <dimension ref="A1:BS13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19351,6 +20595,311 @@
       </c>
       <c r="BS12" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13:19:15</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>21:12</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>02:49</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>06:27</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>06:07</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>21:09</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>22:36</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>76</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>03:53</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>64</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>23:23</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>02:59</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>05:08</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>19:36</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="n">
+        <v>40</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1021</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS13" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -19364,7 +20913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS12"/>
+  <dimension ref="A1:BS13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23143,6 +24692,317 @@
       </c>
       <c r="BS12" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13:19:15</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>22:14</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>02:24</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>21:28</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>04:04</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>23:41</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>03:11</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>05:17</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>19:54</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>57</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN13" t="n">
+        <v>35</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1020</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS13" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -23156,7 +25016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS12"/>
+  <dimension ref="A1:BS13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26935,6 +28795,317 @@
       </c>
       <c r="BS12" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13:19:15</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>21:19</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>02:55</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>02:18</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>22:47</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>03:59</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>63</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>23:33</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>03:05</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>05:13</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>19:46</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>319</v>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN13" t="n">
+        <v>14</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1019</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS13" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -26948,7 +29119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS12"/>
+  <dimension ref="A1:BS13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30709,6 +32880,315 @@
       </c>
       <c r="BS12" t="n">
         <v>200</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13:19:16</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>20:36</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>02:13</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>21:23</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>01:36</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>05:50</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>06:57</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>22:04</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>03:18</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>22:50</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>02:24</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>53</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>51</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ13" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="n">
+        <v>270</v>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN13" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS13" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -30722,7 +33202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS12"/>
+  <dimension ref="A1:BS13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34482,6 +36962,315 @@
         </is>
       </c>
       <c r="BS12" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13:19:16</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>01:32</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>05:54</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>05:33</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>06:59</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>21:53</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>03:17</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>02:21</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>04:34</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>39</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="n">
+        <v>210</v>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN13" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1020</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS13" t="n">
         <v>803</v>
       </c>
     </row>
@@ -34496,7 +37285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS12"/>
+  <dimension ref="A1:BS13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38275,6 +41064,317 @@
       </c>
       <c r="BS12" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13:19:16</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>03:21</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>22:29</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>02:43</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>06:58</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>21:44</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>23:11</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>04:25</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>23:57</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>03:31</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>05:40</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ13" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>51</v>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN13" t="n">
+        <v>50</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1020</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS13" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS13"/>
+  <dimension ref="A1:BS14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4524,6 +4524,317 @@
       </c>
       <c r="BS13" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11:20:22</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>22:36</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>03:40</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>02:01</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>06:17</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>21:14</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>22:33</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>77</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>03:49</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>23:11</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>74</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>02:50</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>05:02</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>83</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>Yuksek</t>
+        </is>
+      </c>
+      <c r="BJ14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>36</v>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN14" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>7191</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS14" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -4537,7 +4848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS13"/>
+  <dimension ref="A1:BS14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8627,6 +8938,317 @@
       </c>
       <c r="BS13" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11:20:23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>03:44</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>21:57</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>06:23</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>06:19</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>22:48</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>03:55</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>23:26</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>02:58</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>05:06</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>48</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>167</v>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>GGD</t>
+        </is>
+      </c>
+      <c r="BN14" t="n">
+        <v>34</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1009</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS14" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -8640,7 +9262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS13"/>
+  <dimension ref="A1:BS14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12730,6 +13352,317 @@
       </c>
       <c r="BS13" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11:20:22</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>22:47</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>03:44</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>22:52</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>03:55</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>63</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>23:29</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>02:59</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>05:05</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>45</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>166</v>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>GGD</t>
+        </is>
+      </c>
+      <c r="BN14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1011</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS14" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -12743,7 +13676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS13"/>
+  <dimension ref="A1:BS14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16833,6 +17766,317 @@
       </c>
       <c r="BS13" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11:20:22</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>03:44</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>21:50</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>02:07</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>06:24</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>21:24</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>22:42</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>03:54</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>23:20</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>02:56</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>05:06</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>16.13</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>66</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ14" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>127</v>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="BN14" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>Hafif yağmur</t>
+        </is>
+      </c>
+      <c r="BS14" t="n">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -16846,7 +18090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS13"/>
+  <dimension ref="A1:BS14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20900,6 +22144,315 @@
       </c>
       <c r="BS13" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11:20:22</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>22:38</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>03:39</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>02:03</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>06:19</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>22:38</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>03:49</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>23:16</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>02:51</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>05:01</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>19:29</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>94</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>Cok Yuksek</t>
+        </is>
+      </c>
+      <c r="BJ14" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="n">
+        <v>110</v>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="BN14" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS14" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -20913,7 +22466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS13"/>
+  <dimension ref="A1:BS14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25003,6 +26556,317 @@
       </c>
       <c r="BS13" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11:20:22</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>22:52</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>03:49</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>02:16</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>21:39</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>22:57</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>63</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>23:34</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>03:04</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>05:10</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>19:46</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ14" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>328</v>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS14" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -25016,7 +26880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS13"/>
+  <dimension ref="A1:BS14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29105,6 +30969,317 @@
         </is>
       </c>
       <c r="BS13" t="n">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11:20:22</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>03:44</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>21:31</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>22:49</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>03:55</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>23:26</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>02:58</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>05:05</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>48</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>192</v>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN14" t="n">
+        <v>19</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1010</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS14" t="n">
         <v>801</v>
       </c>
     </row>
@@ -29119,7 +31294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS13"/>
+  <dimension ref="A1:BS14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33188,6 +35363,315 @@
         </is>
       </c>
       <c r="BS13" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11:20:22</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>22:03</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>03:02</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>01:28</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>05:42</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>05:38</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>20:48</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>03:14</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>22:44</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>02:17</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>53</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>04:25</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>59</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ14" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="n">
+        <v>230</v>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="BN14" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS14" t="n">
         <v>803</v>
       </c>
     </row>
@@ -33202,7 +35686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS13"/>
+  <dimension ref="A1:BS14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37271,6 +39755,311 @@
         </is>
       </c>
       <c r="BS13" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11:20:23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>03:03</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>01:24</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>05:46</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>05:41</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>07:03</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>21:55</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>03:13</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>22:34</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>02:13</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>04:26</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS14" t="n">
         <v>803</v>
       </c>
     </row>
@@ -37285,7 +40074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS13"/>
+  <dimension ref="A1:BS14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41375,6 +44164,317 @@
       </c>
       <c r="BS13" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11:20:23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>23:12</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>06:46</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>21:55</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>23:13</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>04:21</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>64</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>23:51</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>03:24</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>05:32</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>54</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>16</v>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>181</v>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BN14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS14" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS14"/>
+  <dimension ref="A1:BS15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4835,6 +4835,317 @@
       </c>
       <c r="BS14" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>17:08:16</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>93</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>22:36</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>03:40</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>02:01</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>06:17</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>21:14</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>22:33</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>03:49</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>23:11</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>74</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>02:50</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>05:02</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>157</v>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>GGD</t>
+        </is>
+      </c>
+      <c r="BN15" t="n">
+        <v>33</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1011</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS15" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -4848,7 +5159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS14"/>
+  <dimension ref="A1:BS15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9249,6 +9560,317 @@
       </c>
       <c r="BS14" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>17:08:17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>93</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>03:44</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>21:57</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>06:23</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>06:19</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>22:48</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>03:55</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>23:26</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>02:58</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>05:06</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>66</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ15" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>266</v>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN15" t="n">
+        <v>58</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1009</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS15" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -9262,7 +9884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS14"/>
+  <dimension ref="A1:BS15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13663,6 +14285,317 @@
       </c>
       <c r="BS14" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>17:08:16</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>93</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>22:47</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>03:44</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>22:52</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>03:55</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>63</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>23:29</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>02:59</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>05:05</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>68</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ15" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>31</v>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN15" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1011</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>Hafif yağmur</t>
+        </is>
+      </c>
+      <c r="BS15" t="n">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -13676,7 +14609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS14"/>
+  <dimension ref="A1:BS15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18077,6 +19010,317 @@
       </c>
       <c r="BS14" t="n">
         <v>500</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>17:08:16</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>64</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>93</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>03:44</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>21:50</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>02:07</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>06:24</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>21:24</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>22:42</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>76</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>03:54</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>23:20</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>73</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>02:56</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>05:06</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>43</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ15" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>89</v>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BN15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1009</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS15" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -18090,7 +19334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS14"/>
+  <dimension ref="A1:BS15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22452,6 +23696,315 @@
         </is>
       </c>
       <c r="BS14" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>17:08:16</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>93</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>22:38</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>03:39</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>02:03</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>06:19</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>22:38</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>03:49</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>23:16</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>02:51</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>05:01</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>19:29</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ15" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="n">
+        <v>100</v>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BN15" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS15" t="n">
         <v>803</v>
       </c>
     </row>
@@ -22466,7 +24019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS14"/>
+  <dimension ref="A1:BS15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26867,6 +28420,317 @@
       </c>
       <c r="BS14" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>17:08:17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>93</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>22:52</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>03:49</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>02:16</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>21:39</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>22:57</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>63</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>23:34</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>03:04</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>05:10</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>19:46</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>68</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>164</v>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>GGD</t>
+        </is>
+      </c>
+      <c r="BN15" t="n">
+        <v>99</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS15" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -26880,7 +28744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS14"/>
+  <dimension ref="A1:BS15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31281,6 +33145,317 @@
       </c>
       <c r="BS14" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>17:08:17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>93</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>03:44</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>21:31</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>22:49</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>03:55</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>23:26</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>02:58</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>05:05</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>57</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ15" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>347</v>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN15" t="n">
+        <v>95</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1010</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS15" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -31294,7 +33469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS14"/>
+  <dimension ref="A1:BS15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35672,6 +37847,315 @@
         </is>
       </c>
       <c r="BS14" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>17:08:17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>93</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>22:03</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>03:02</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>01:28</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>05:42</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>05:38</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>20:48</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>03:14</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>22:44</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>02:17</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>53</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>04:25</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="n">
+        <v>300</v>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>KBB</t>
+        </is>
+      </c>
+      <c r="BN15" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS15" t="n">
         <v>803</v>
       </c>
     </row>
@@ -35686,7 +38170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS14"/>
+  <dimension ref="A1:BS15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40060,6 +42544,311 @@
         </is>
       </c>
       <c r="BS14" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>17:08:17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>93</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>03:03</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>01:24</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>05:46</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>05:41</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>07:03</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>21:55</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>03:13</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>22:34</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>02:13</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>04:26</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>21.93</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>27</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS15" t="n">
         <v>803</v>
       </c>
     </row>
@@ -40074,7 +42863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS14"/>
+  <dimension ref="A1:BS15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44475,6 +47264,317 @@
       </c>
       <c r="BS14" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>17:08:17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>93</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>23:12</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>06:46</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>21:55</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>23:13</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>04:21</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>64</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>23:51</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>03:24</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>05:32</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>64</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ15" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>288</v>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>KBB</t>
+        </is>
+      </c>
+      <c r="BN15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1010</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS15" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS15"/>
+  <dimension ref="A1:BS16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5146,6 +5146,317 @@
       </c>
       <c r="BS15" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>08:21:08</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>23:22</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>04:12</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>01:57</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>21:19</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>22:34</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>03:47</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>23:08</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>74</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>02:46</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>04:58</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>85</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>Yuksek</t>
+        </is>
+      </c>
+      <c r="BJ16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>291</v>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>KBB</t>
+        </is>
+      </c>
+      <c r="BN16" t="n">
+        <v>82</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS16" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -5159,7 +5470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS15"/>
+  <dimension ref="A1:BS16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9871,6 +10182,317 @@
       </c>
       <c r="BS15" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>08:21:09</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>23:31</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>21:53</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>02:06</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>06:19</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>22:49</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>03:53</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>23:23</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>02:54</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>05:02</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>81</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>344</v>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1010</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS16" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -9884,7 +10506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS15"/>
+  <dimension ref="A1:BS16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14596,6 +15218,317 @@
       </c>
       <c r="BS15" t="n">
         <v>500</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>08:21:08</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>23:33</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>04:14</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>21:57</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>02:07</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>06:17</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>21:39</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>03:53</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>63</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>23:26</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>02:55</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>05:01</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>84</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>Yuksek</t>
+        </is>
+      </c>
+      <c r="BJ16" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>323</v>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN16" t="n">
+        <v>57</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS16" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -14609,7 +15542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS15"/>
+  <dimension ref="A1:BS16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19321,6 +20254,317 @@
       </c>
       <c r="BS15" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>08:21:08</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>23:29</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>04:16</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>02:03</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>06:24</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>76</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>03:52</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>23:17</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>73</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>02:52</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>05:02</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>19:29</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>75</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ16" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>324</v>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN16" t="n">
+        <v>19</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS16" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -19334,7 +20578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS15"/>
+  <dimension ref="A1:BS16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24005,6 +25249,315 @@
         </is>
       </c>
       <c r="BS15" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>08:21:08</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>23:24</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>04:10</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>21:42</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>01:59</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>21:25</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>07:38</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>22:39</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>03:47</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>23:13</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>02:48</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>04:57</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>88</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>Yuksek</t>
+        </is>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="n">
+        <v>270</v>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN16" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS16" t="n">
         <v>803</v>
       </c>
     </row>
@@ -24019,7 +25572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS15"/>
+  <dimension ref="A1:BS16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28730,6 +30283,317 @@
         </is>
       </c>
       <c r="BS15" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>08:21:08</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>23:38</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>04:19</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>02:12</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>21:44</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>22:58</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>03:58</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>63</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>23:31</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>05:06</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>19:43</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>87</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>Yuksek</t>
+        </is>
+      </c>
+      <c r="BJ16" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>349</v>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN16" t="n">
+        <v>93</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS16" t="n">
         <v>804</v>
       </c>
     </row>
@@ -28744,7 +30608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS15"/>
+  <dimension ref="A1:BS16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33456,6 +35320,317 @@
       </c>
       <c r="BS15" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>08:21:08</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>23:31</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>04:14</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>02:06</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>22:50</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>03:53</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>23:23</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>02:54</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>05:02</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>81</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1010</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS16" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -33469,7 +35644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS15"/>
+  <dimension ref="A1:BS16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38156,6 +40331,315 @@
         </is>
       </c>
       <c r="BS15" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>08:21:09</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>22:49</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>03:33</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>21:11</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>01:24</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>05:38</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>05:41</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>22:07</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>03:12</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>02:13</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>53</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>04:21</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>82</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="n">
+        <v>360</v>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN16" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1008</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS16" t="n">
         <v>803</v>
       </c>
     </row>
@@ -38170,7 +40654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS15"/>
+  <dimension ref="A1:BS16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42849,6 +45333,315 @@
         </is>
       </c>
       <c r="BS15" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>08:21:09</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>22:44</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>03:35</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>01:20</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>05:42</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>05:44</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>20:42</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>07:04</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>21:56</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>03:11</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>22:31</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>04:22</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>39</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="n">
+        <v>220</v>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="BN16" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>8000</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS16" t="n">
         <v>803</v>
       </c>
     </row>
@@ -42863,7 +45656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS15"/>
+  <dimension ref="A1:BS16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47575,6 +50368,317 @@
       </c>
       <c r="BS15" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>08:21:09</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>23:58</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>04:42</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>22:17</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>02:32</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>06:46</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>06:49</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>23:14</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>04:19</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>64</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>23:47</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>03:20</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>05:29</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>76</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ16" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>23</v>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN16" t="n">
+        <v>25</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS16" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS16"/>
+  <dimension ref="A1:BS17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5457,6 +5457,317 @@
       </c>
       <c r="BS16" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>21:43:56</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>01:01</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>05:34</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>21:24</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>01:49</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>06:28</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>21:31</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>22:35</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>03:44</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>23:02</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>02:39</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>04:51</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>63</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>144</v>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS17" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -5470,7 +5781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS16"/>
+  <dimension ref="A1:BS17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10493,6 +10804,317 @@
       </c>
       <c r="BS16" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>21:43:59</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>21:38</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>01:10</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>05:35</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>01:58</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>06:29</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>21:44</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>22:51</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>03:49</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>23:16</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>02:47</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>04:55</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>54</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN17" t="n">
+        <v>28</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS17" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -10506,7 +11128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS16"/>
+  <dimension ref="A1:BS17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15529,6 +16151,317 @@
       </c>
       <c r="BS16" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>21:43:57</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>21:42</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>01:11</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>05:33</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>21:49</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>01:59</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>06:09</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>06:28</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>21:47</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>22:54</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>03:49</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>23:19</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>02:48</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>04:54</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>66</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>341</v>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN17" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS17" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -15542,7 +16475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS16"/>
+  <dimension ref="A1:BS17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20565,6 +21498,317 @@
       </c>
       <c r="BS16" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>21:43:57</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>21:31</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>01:08</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>05:37</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>01:55</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>06:13</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>21:41</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>03:48</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>02:45</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>54</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>04:55</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ17" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>113</v>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="BN17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS17" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -20578,7 +21822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS16"/>
+  <dimension ref="A1:BS17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25559,6 +26803,315 @@
       </c>
       <c r="BS16" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>21:43:57</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>21:27</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>01:03</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>05:31</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>01:51</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>06:07</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>21:37</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>03:43</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>23:06</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>02:40</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>04:50</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>19:14</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>67</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="n">
+        <v>240</v>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS17" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -25572,7 +27125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS16"/>
+  <dimension ref="A1:BS17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30594,6 +32147,317 @@
         </is>
       </c>
       <c r="BS16" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>21:43:58</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>21:47</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>01:17</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>05:38</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>02:04</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>06:14</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>22:59</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>03:54</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>23:24</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>02:53</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>04:59</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>75</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>103</v>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="BN17" t="n">
+        <v>99</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS17" t="n">
         <v>804</v>
       </c>
     </row>
@@ -30608,7 +32472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS16"/>
+  <dimension ref="A1:BS17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35631,6 +37495,317 @@
       </c>
       <c r="BS16" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>21:43:58</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>21:39</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>01:10</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>05:34</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>01:58</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>06:29</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>21:44</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>22:51</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>03:49</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>23:17</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>02:47</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>04:54</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>15.73</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>14.28</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>48</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>162</v>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>GGD</t>
+        </is>
+      </c>
+      <c r="BN17" t="n">
+        <v>72</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS17" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -35644,7 +37819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS16"/>
+  <dimension ref="A1:BS17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40641,6 +42816,317 @@
       </c>
       <c r="BS16" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>21:43:58</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>00:27</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>04:53</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>01:17</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>22:09</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>03:08</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>22:34</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>02:05</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>04:13</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>159</v>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>GGD</t>
+        </is>
+      </c>
+      <c r="BN17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS17" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -40654,7 +43140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS16"/>
+  <dimension ref="A1:BS17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45643,6 +48129,317 @@
       </c>
       <c r="BS16" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>21:43:58</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>65</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20:42</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>00:23</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>04:57</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>01:13</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>05:34</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>05:52</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>78</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>07:08</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>03:07</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>22:24</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>02:02</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>62</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>189</v>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1019</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS17" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -45656,7 +48453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS16"/>
+  <dimension ref="A1:BS17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50679,6 +53476,317 @@
       </c>
       <c r="BS16" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>21:43:59</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>22:03</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>01:37</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>06:03</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>22:09</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>02:24</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>06:38</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>06:57</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>23:41</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>03:13</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>05:21</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>77</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>325</v>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS17" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS17"/>
+  <dimension ref="A1:BS18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5767,6 +5767,317 @@
         </is>
       </c>
       <c r="BS17" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07:52:47</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>65</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>01:52</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>21:24</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>21:31</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>22:36</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>03:42</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>22:58</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>04:47</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>49</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>241</v>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS18" t="n">
         <v>800</v>
       </c>
     </row>
@@ -5781,7 +6092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS17"/>
+  <dimension ref="A1:BS18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11115,6 +11426,317 @@
       </c>
       <c r="BS17" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07:52:48</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>21:38</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>02:02</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>21:41</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>01:54</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>06:07</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>21:47</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>22:51</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>03:47</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>23:13</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>02:43</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>04:51</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>77</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>248</v>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN18" t="n">
+        <v>58</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS18" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -11128,7 +11750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS17"/>
+  <dimension ref="A1:BS18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16462,6 +17084,317 @@
       </c>
       <c r="BS17" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07:52:47</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>21:42</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>02:03</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>06:24</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>01:55</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>21:51</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>03:47</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>23:16</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>02:44</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>04:50</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>66</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>220</v>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="BN18" t="n">
+        <v>35</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS18" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -16475,7 +17408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS17"/>
+  <dimension ref="A1:BS18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21808,6 +22741,317 @@
         </is>
       </c>
       <c r="BS17" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07:52:47</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>21:31</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>01:59</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>06:28</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>01:52</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>06:09</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>21:41</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>03:46</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>23:07</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>02:41</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>54</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>04:51</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ18" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>305</v>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS18" t="n">
         <v>800</v>
       </c>
     </row>
@@ -21822,7 +23066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS17"/>
+  <dimension ref="A1:BS18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27112,6 +28356,315 @@
       </c>
       <c r="BS17" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07:52:47</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>53</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>21:27</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>01:54</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>01:47</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>06:03</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>06:29</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>21:37</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>03:42</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>23:03</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>04:46</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>19:14</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>76</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ18" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="n">
+        <v>90</v>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BN18" t="n">
+        <v>20</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS18" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -27125,7 +28678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS17"/>
+  <dimension ref="A1:BS18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32459,6 +34012,317 @@
       </c>
       <c r="BS17" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07:52:47</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>21:47</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>02:08</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>06:29</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>21:50</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>06:37</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>21:56</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>03:52</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>08:37</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>23:21</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>02:49</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>04:55</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>245</v>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS18" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -32472,7 +34336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS17"/>
+  <dimension ref="A1:BS18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37805,6 +39669,317 @@
         </is>
       </c>
       <c r="BS17" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07:52:48</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>21:39</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>02:02</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>21:42</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>01:54</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>21:48</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>22:52</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>03:47</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>23:13</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>02:43</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>04:50</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>64</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>253</v>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN18" t="n">
+        <v>56</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS18" t="n">
         <v>803</v>
       </c>
     </row>
@@ -37819,7 +39994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS17"/>
+  <dimension ref="A1:BS18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43126,6 +45301,311 @@
         </is>
       </c>
       <c r="BS17" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07:52:48</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>01:18</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>05:43</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>01:13</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>05:26</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>05:52</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>07:07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>22:09</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>03:06</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>22:31</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>02:02</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>04:10</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>76</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS18" t="n">
         <v>800</v>
       </c>
     </row>
@@ -43140,7 +45620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS17"/>
+  <dimension ref="A1:BS18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48439,6 +50919,317 @@
         </is>
       </c>
       <c r="BS17" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07:52:48</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20:42</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>01:14</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>05:47</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>01:09</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>05:55</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>78</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>07:09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>21:59</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>03:06</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>01:59</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>41</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>210</v>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS18" t="n">
         <v>800</v>
       </c>
     </row>
@@ -48453,7 +51244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS17"/>
+  <dimension ref="A1:BS18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53786,6 +56577,317 @@
         </is>
       </c>
       <c r="BS17" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07:52:48</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>22:03</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>02:28</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>02:20</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>23:16</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>04:13</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>23:37</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>03:09</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>05:17</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>21.03</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>21.03</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>21.03</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>74</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ18" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>105</v>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="BN18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS18" t="n">
         <v>800</v>
       </c>
     </row>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS18"/>
+  <dimension ref="A1:BS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6078,6 +6078,317 @@
         </is>
       </c>
       <c r="BS18" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11:27:07</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>01:52</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>21:24</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>21:31</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>22:36</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>03:42</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>22:58</t>
+        </is>
+      </c>
+      <c r="AN19" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>04:47</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>44</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>248</v>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN19" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS19" t="n">
         <v>800</v>
       </c>
     </row>
@@ -6092,7 +6403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS18"/>
+  <dimension ref="A1:BS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11737,6 +12048,317 @@
       </c>
       <c r="BS18" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11:27:10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>21:38</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>02:02</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>21:41</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>01:54</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>06:07</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>21:47</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>22:51</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>03:47</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>23:13</t>
+        </is>
+      </c>
+      <c r="AN19" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>02:43</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>53</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>04:51</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>45</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>200</v>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS19" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -11750,7 +12372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS18"/>
+  <dimension ref="A1:BS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17394,6 +18016,317 @@
         </is>
       </c>
       <c r="BS18" t="n">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11:27:08</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>21:42</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>02:03</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>06:24</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>01:55</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>21:51</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>03:47</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>64</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>23:16</t>
+        </is>
+      </c>
+      <c r="AN19" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>02:44</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>04:50</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>51</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ19" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>222</v>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="BN19" t="n">
+        <v>36</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS19" t="n">
         <v>802</v>
       </c>
     </row>
@@ -17408,7 +18341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS18"/>
+  <dimension ref="A1:BS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23052,6 +23985,317 @@
         </is>
       </c>
       <c r="BS18" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11:27:09</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>21:31</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>01:59</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>06:28</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>01:52</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>06:09</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>21:41</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>03:46</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>23:07</t>
+        </is>
+      </c>
+      <c r="AN19" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>02:41</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>04:51</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>43</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>296</v>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>KBB</t>
+        </is>
+      </c>
+      <c r="BN19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS19" t="n">
         <v>800</v>
       </c>
     </row>
@@ -23066,7 +24310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS18"/>
+  <dimension ref="A1:BS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28664,6 +29908,315 @@
         </is>
       </c>
       <c r="BS18" t="n">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11:27:09</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>21:27</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>01:54</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>01:47</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>06:03</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>06:29</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>21:37</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>03:42</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>23:03</t>
+        </is>
+      </c>
+      <c r="AN19" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>04:46</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>19:14</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>49</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="n">
+        <v>300</v>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>KBB</t>
+        </is>
+      </c>
+      <c r="BN19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS19" t="n">
         <v>801</v>
       </c>
     </row>
@@ -28678,7 +30231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS18"/>
+  <dimension ref="A1:BS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34322,6 +35875,317 @@
         </is>
       </c>
       <c r="BS18" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11:27:09</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>21:47</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>02:08</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>06:29</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>21:50</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>06:37</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>21:56</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>03:52</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>23:21</t>
+        </is>
+      </c>
+      <c r="AN19" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>02:49</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>04:55</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>53</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ19" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>276</v>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN19" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS19" t="n">
         <v>800</v>
       </c>
     </row>
@@ -34336,7 +36200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS18"/>
+  <dimension ref="A1:BS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39981,6 +41845,317 @@
       </c>
       <c r="BS18" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11:27:09</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>21:39</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>02:02</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>21:42</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>01:54</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>21:48</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>22:52</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>03:47</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>23:13</t>
+        </is>
+      </c>
+      <c r="AN19" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>02:43</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>04:50</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>20.62</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>20.21</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>22.06</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>47</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>256</v>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS19" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -39994,7 +42169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS18"/>
+  <dimension ref="A1:BS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45607,6 +47782,315 @@
       </c>
       <c r="BS18" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11:27:09</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>01:18</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>05:43</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>01:13</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>05:26</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>05:52</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>07:07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>22:09</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>03:06</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>22:31</t>
+        </is>
+      </c>
+      <c r="AN19" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>02:02</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>04:10</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>41</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ19" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="n">
+        <v>230</v>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="BN19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS19" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -45620,7 +48104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS18"/>
+  <dimension ref="A1:BS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51231,6 +53715,311 @@
       </c>
       <c r="BS18" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11:27:09</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20:42</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>01:14</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>05:47</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>01:09</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>05:55</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>78</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>07:09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>21:59</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>03:06</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
+      </c>
+      <c r="AN19" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>01:59</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS19" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -51244,7 +54033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS18"/>
+  <dimension ref="A1:BS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56889,6 +59678,317 @@
       </c>
       <c r="BS18" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11:27:09</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>99</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Yeni Ay</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Gozlem Icin Ideal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>22:03</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>02:28</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>02:20</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>23:16</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>04:13</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>23:37</t>
+        </is>
+      </c>
+      <c r="AN19" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>03:09</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>05:17</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>67</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ19" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>108</v>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="BN19" t="n">
+        <v>24</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS19" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS19"/>
+  <dimension ref="A1:BS20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6389,6 +6389,317 @@
         </is>
       </c>
       <c r="BS19" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>09:54:23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>02:43</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>01:41</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>06:35</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>22:37</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>03:40</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>02:31</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>04:43</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>49</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>319</v>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN20" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1019</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS20" t="n">
         <v>800</v>
       </c>
     </row>
@@ -6403,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS19"/>
+  <dimension ref="A1:BS20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12359,6 +12670,317 @@
       </c>
       <c r="BS19" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>09:54:25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>22:25</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>02:53</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>07:23</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>21:37</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>01:50</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>06:03</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>21:51</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>22:52</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>23:09</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>02:39</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>53</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>04:47</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>260</v>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN20" t="n">
+        <v>12</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS20" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -12372,7 +12994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS19"/>
+  <dimension ref="A1:BS20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18328,6 +18950,317 @@
       </c>
       <c r="BS19" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>09:54:23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>22:29</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>02:54</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>21:41</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>01:51</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>06:35</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>64</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>23:13</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>02:40</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>04:46</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ20" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>178</v>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BN20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS20" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -18341,7 +19274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS19"/>
+  <dimension ref="A1:BS20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24297,6 +25230,317 @@
       </c>
       <c r="BS19" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>09:54:24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>52</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>22:18</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>02:50</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>01:48</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>06:38</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>21:44</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>22:46</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>23:04</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>04:47</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>48</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>90</v>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BN20" t="n">
+        <v>46</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS20" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -24310,7 +25554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS19"/>
+  <dimension ref="A1:BS20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30218,6 +31462,315 @@
       </c>
       <c r="BS19" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>09:54:24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>22:14</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>02:45</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>21:27</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>01:43</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>05:59</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>22:42</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>03:40</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>02:33</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>04:42</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>63</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="n">
+        <v>90</v>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1019</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS20" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -30231,7 +31784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS19"/>
+  <dimension ref="A1:BS20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36186,6 +37739,317 @@
         </is>
       </c>
       <c r="BS19" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>09:54:24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>22:34</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>02:59</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>07:27</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>01:56</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>21:59</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>23:01</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>03:50</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>23:18</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>02:45</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>04:51</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>19.53</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>184</v>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BN20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS20" t="n">
         <v>800</v>
       </c>
     </row>
@@ -36200,7 +38064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS19"/>
+  <dimension ref="A1:BS20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42156,6 +44020,317 @@
       </c>
       <c r="BS19" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>09:54:24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>22:26</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>02:53</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>21:38</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>01:50</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>21:51</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>02:39</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>04:47</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>240</v>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN20" t="n">
+        <v>27</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS20" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -42169,7 +44344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS19"/>
+  <dimension ref="A1:BS20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48091,6 +50266,315 @@
       </c>
       <c r="BS19" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>09:54:24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>21:42</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>01:09</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>05:22</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>05:55</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>07:08</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>22:10</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>03:04</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>22:28</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>01:58</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>04:06</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ20" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="n">
+        <v>230</v>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="BN20" t="n">
+        <v>40</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS20" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -48104,7 +50588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS19"/>
+  <dimension ref="A1:BS20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54020,6 +56504,311 @@
       </c>
       <c r="BS19" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>09:54:24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>02:05</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>01:05</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>05:26</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>05:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>20:57</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>78</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>21:59</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>03:04</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>22:18</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>01:55</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>04:07</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>48</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="n">
+        <v>40</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS20" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -54033,7 +56822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS19"/>
+  <dimension ref="A1:BS20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59989,6 +62778,317 @@
       </c>
       <c r="BS19" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>09:54:24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>22:50</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>03:19</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>02:16</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>07:04</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>23:17</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>23:34</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>03:05</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>05:14</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>63</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ20" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>108</v>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="BN20" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS20" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS20"/>
+  <dimension ref="A1:BS21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6701,6 +6701,317 @@
       </c>
       <c r="BS20" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>16:30:28</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>45</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>02:43</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>01:41</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>06:35</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>22:37</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>03:40</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>02:31</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>04:43</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>194</v>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN21" t="n">
+        <v>61</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS21" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -6714,7 +7025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS20"/>
+  <dimension ref="A1:BS21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12981,6 +13292,317 @@
       </c>
       <c r="BS20" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>16:30:30</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>22:25</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>02:53</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>07:23</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>21:37</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>01:50</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>06:03</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>21:51</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>22:52</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>23:09</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>02:39</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
+        <v>53</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>04:47</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>261</v>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN21" t="n">
+        <v>89</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS21" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -12994,7 +13616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS20"/>
+  <dimension ref="A1:BS21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19261,6 +19883,317 @@
       </c>
       <c r="BS20" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>16:30:28</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>22:29</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>02:54</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>21:41</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>01:51</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>06:35</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>23:13</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>02:40</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>04:46</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>70</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>9</v>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN21" t="n">
+        <v>97</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS21" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -19274,7 +20207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS20"/>
+  <dimension ref="A1:BS21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25541,6 +26474,317 @@
       </c>
       <c r="BS20" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>16:30:28</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>22:18</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>02:50</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>01:48</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>06:38</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>21:44</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>22:46</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>66</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>23:04</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>04:47</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ21" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>34</v>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS21" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -25554,7 +26798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS20"/>
+  <dimension ref="A1:BS21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31771,6 +33015,315 @@
       </c>
       <c r="BS20" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>16:30:29</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>22:14</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>02:45</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>21:27</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>01:43</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>05:59</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>22:42</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>03:40</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>02:33</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>04:42</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ21" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="n">
+        <v>300</v>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>KBB</t>
+        </is>
+      </c>
+      <c r="BN21" t="n">
+        <v>40</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS21" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -31784,7 +33337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS20"/>
+  <dimension ref="A1:BS21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38051,6 +39604,317 @@
       </c>
       <c r="BS20" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>16:30:29</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>22:34</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>02:59</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>07:27</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>01:56</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>21:59</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>75</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>23:01</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>03:50</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>23:18</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>02:45</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>04:51</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>24.36</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>331</v>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN21" t="n">
+        <v>84</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS21" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -38064,7 +39928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS20"/>
+  <dimension ref="A1:BS21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44331,6 +46195,317 @@
       </c>
       <c r="BS20" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>16:30:29</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>22:26</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>02:53</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>21:38</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>01:50</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>21:51</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>02:39</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>04:47</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ21" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>275</v>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN21" t="n">
+        <v>70</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS21" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -44344,7 +46519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS20"/>
+  <dimension ref="A1:BS21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50575,6 +52750,315 @@
       </c>
       <c r="BS20" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>16:30:29</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>21:42</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>01:09</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>05:22</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>05:55</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>07:08</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>22:10</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>03:04</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>22:28</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>01:58</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>04:06</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>37</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ21" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="n">
+        <v>260</v>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN21" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS21" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -50588,7 +53072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS20"/>
+  <dimension ref="A1:BS21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56808,6 +59292,315 @@
         </is>
       </c>
       <c r="BS20" t="n">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>16:30:29</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>02:05</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>01:05</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>05:26</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>05:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>20:57</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>78</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>21:59</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>03:04</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>22:18</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>74</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>01:55</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>04:07</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>35</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ21" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="n">
+        <v>210</v>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN21" t="n">
+        <v>40</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS21" t="n">
         <v>802</v>
       </c>
     </row>
@@ -56822,7 +59615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS20"/>
+  <dimension ref="A1:BS21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63089,6 +65882,317 @@
       </c>
       <c r="BS20" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>16:30:29</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>22:50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>03:19</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>02:16</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>07:04</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>23:17</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>23:34</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>03:05</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>05:14</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>71</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>27.02</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ21" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>238</v>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN21" t="n">
+        <v>75</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS21" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS21"/>
+  <dimension ref="A1:BS22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7012,6 +7012,317 @@
       </c>
       <c r="BS21" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>10:34:01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>22:49</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>03:33</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>21:17</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>01:37</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>05:58</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>06:38</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>21:38</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>22:37</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>03:38</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>22:52</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>02:28</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AT22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>04:40</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>48</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>268</v>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN22" t="n">
+        <v>16</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS22" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -7025,7 +7336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS21"/>
+  <dimension ref="A1:BS22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13603,6 +13914,317 @@
       </c>
       <c r="BS21" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>10:34:02</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>23:05</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>03:42</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>21:33</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>01:46</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>05:59</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>03:43</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>23:06</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AT22" t="n">
+        <v>53</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>04:43</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>48</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>11</v>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ22" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>337</v>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN22" t="n">
+        <v>36</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS22" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -13616,7 +14238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS21"/>
+  <dimension ref="A1:BS22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20194,6 +20816,317 @@
       </c>
       <c r="BS21" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>10:34:01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>46</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>23:09</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>03:43</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>21:37</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>01:47</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>05:57</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>21:57</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>22:56</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>03:43</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>23:09</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AT22" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>04:43</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>70</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>207</v>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN22" t="n">
+        <v>54</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS22" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -20207,7 +21140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS21"/>
+  <dimension ref="A1:BS22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26784,6 +27717,317 @@
         </is>
       </c>
       <c r="BS21" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>10:34:01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>22:59</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>03:40</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>01:44</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>21:47</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>22:47</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>03:43</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>66</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>23:01</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>02:34</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AT22" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>04:44</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ22" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>213</v>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS22" t="n">
         <v>800</v>
       </c>
     </row>
@@ -26798,7 +28042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS21"/>
+  <dimension ref="A1:BS22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33324,6 +34568,317 @@
       </c>
       <c r="BS21" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>10:34:01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>03:35</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>21:23</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>01:39</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>05:56</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>21:43</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>03:38</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>66</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>22:57</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>02:29</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AT22" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>04:39</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>39</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>213</v>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN22" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS22" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -33337,7 +34892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS21"/>
+  <dimension ref="A1:BS22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39915,6 +41470,317 @@
       </c>
       <c r="BS21" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>10:34:02</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>23:14</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>03:49</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>21:42</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>01:52</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>75</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>23:01</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>03:48</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>23:14</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>02:42</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AT22" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>04:48</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ22" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>246</v>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN22" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS22" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -39928,7 +41794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS21"/>
+  <dimension ref="A1:BS22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46505,6 +48371,317 @@
         </is>
       </c>
       <c r="BS21" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>10:34:02</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>23:06</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>03:42</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>01:46</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>05:58</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>03:43</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>23:07</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AT22" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>04:43</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>20.73</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>63</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>250</v>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN22" t="n">
+        <v>70</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS22" t="n">
         <v>803</v>
       </c>
     </row>
@@ -46519,7 +48696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS21"/>
+  <dimension ref="A1:BS22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53059,6 +55236,317 @@
       </c>
       <c r="BS21" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>10:34:02</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>22:22</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>02:59</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>01:05</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>05:18</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>05:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>21:11</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>22:10</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>03:02</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>22:24</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>01:54</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AT22" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>04:02</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>39</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ22" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>272</v>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS22" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -53072,7 +55560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS21"/>
+  <dimension ref="A1:BS22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59601,6 +62089,317 @@
         </is>
       </c>
       <c r="BS21" t="n">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>10:34:02</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>02:55</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>20:39</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>01:01</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>05:22</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>78</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>07:13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>03:02</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>22:14</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>74</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>01:51</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AT22" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>04:04</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>37</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>198</v>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN22" t="n">
+        <v>42</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS22" t="n">
         <v>802</v>
       </c>
     </row>
@@ -59615,7 +62414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS21"/>
+  <dimension ref="A1:BS22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66193,6 +68992,317 @@
       </c>
       <c r="BS21" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>10:34:02</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>23:31</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>04:09</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>02:12</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>07:07</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>22:18</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>23:17</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>04:10</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>23:31</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>03:02</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AT22" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>05:10</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>71</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
+        <v>26.58</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>26.58</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>26.58</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>26.58</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>45</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ22" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>115</v>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="BN22" t="n">
+        <v>22</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS22" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS22"/>
+  <dimension ref="A1:BS23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7323,6 +7323,317 @@
       </c>
       <c r="BS22" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15:07:17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>23:24</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>04:21</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>01:33</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>05:54</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>22:38</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>03:36</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>22:49</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>02:24</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AT23" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>04:36</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC23" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>283</v>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>KBB</t>
+        </is>
+      </c>
+      <c r="BN23" t="n">
+        <v>56</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS23" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -7336,7 +7647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS22"/>
+  <dimension ref="A1:BS23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14225,6 +14536,317 @@
       </c>
       <c r="BS22" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15:07:18</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>23:39</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>01:42</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>05:55</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>21:56</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>03:41</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>23:03</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>02:32</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AT23" t="n">
+        <v>53</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>04:40</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC23" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>24.81</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>33</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ23" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>269</v>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN23" t="n">
+        <v>14</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1008</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS23" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -14238,7 +14860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS22"/>
+  <dimension ref="A1:BS23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21127,6 +21749,317 @@
       </c>
       <c r="BS22" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15:07:17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>23:42</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>04:31</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>21:33</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>01:43</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>05:53</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>22:56</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>03:41</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>23:06</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>02:33</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AT23" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>04:39</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>70</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC23" t="n">
+        <v>24.13</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>24.13</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>24.13</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ23" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>206</v>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN23" t="n">
+        <v>17</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS23" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -21140,7 +22073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS22"/>
+  <dimension ref="A1:BS23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28028,6 +28961,317 @@
         </is>
       </c>
       <c r="BS22" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15:07:17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>23:33</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>04:27</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>21:23</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>05:57</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>21:50</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>22:47</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>03:41</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>22:57</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AT23" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>04:40</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC23" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>25.31</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>33</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ23" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>352</v>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS23" t="n">
         <v>800</v>
       </c>
     </row>
@@ -28042,7 +29286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS22"/>
+  <dimension ref="A1:BS23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34879,6 +36123,317 @@
       </c>
       <c r="BS22" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15:07:17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>65</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>23:29</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>04:23</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>21:19</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>01:35</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>05:52</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>03:36</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>02:25</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AT23" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>04:35</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC23" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>29</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>60</v>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BN23" t="n">
+        <v>26</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1011</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS23" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -34892,7 +36447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS22"/>
+  <dimension ref="A1:BS23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41781,6 +43336,317 @@
       </c>
       <c r="BS22" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15:07:17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>23:47</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>04:36</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>21:39</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>01:48</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>05:58</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>06:47</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>23:02</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>03:46</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>23:11</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AT23" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>04:44</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC23" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>243</v>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS23" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -41794,7 +43660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS22"/>
+  <dimension ref="A1:BS23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48683,6 +50549,317 @@
       </c>
       <c r="BS22" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15:07:18</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>23:39</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>01:42</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>05:54</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>21:57</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>22:54</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>03:41</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>23:03</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>02:32</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AT23" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>04:39</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC23" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>28.17</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ23" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>266</v>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1008</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS23" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -48696,7 +50873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS22"/>
+  <dimension ref="A1:BS23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55547,6 +57724,317 @@
       </c>
       <c r="BS22" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15:07:18</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>22:56</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>03:47</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>01:01</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>05:14</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>21:14</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>01:51</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AT23" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>03:59</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC23" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>39</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ23" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>276</v>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN23" t="n">
+        <v>19</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1011</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS23" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -55560,7 +58048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS22"/>
+  <dimension ref="A1:BS23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62400,6 +64888,317 @@
         </is>
       </c>
       <c r="BS22" t="n">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15:07:18</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>22:46</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>03:43</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>00:57</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>05:19</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>74</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>01:47</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AT23" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC23" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>38</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ23" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>208</v>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN23" t="n">
+        <v>28</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS23" t="n">
         <v>802</v>
       </c>
     </row>
@@ -62414,7 +65213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS22"/>
+  <dimension ref="A1:BS23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69303,6 +72102,317 @@
       </c>
       <c r="BS22" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15:07:18</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>60</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hilal (Azalan)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>00:04</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>04:56</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>02:08</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>23:18</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>04:08</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>23:28</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>02:58</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AT23" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>05:06</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>19:37</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>71</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC23" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>28.55</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>48</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>135</v>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="BN23" t="n">
+        <v>25</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1011</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS23" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS23"/>
+  <dimension ref="A1:BS24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7634,6 +7634,317 @@
       </c>
       <c r="BS23" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09:18:51</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>00:45</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>01:22</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>05:42</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>22:39</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>03:31</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>22:39</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>02:13</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>04:25</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="AZ24" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC24" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>56</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>332</v>
+      </c>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS24" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -7647,7 +7958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS23"/>
+  <dimension ref="A1:BS24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14846,6 +15157,317 @@
         </is>
       </c>
       <c r="BS23" t="n">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09:18:52</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>00:55</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>05:43</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>22:54</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>03:36</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>02:21</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>04:28</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AZ24" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC24" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>53</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>285</v>
+      </c>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>KBB</t>
+        </is>
+      </c>
+      <c r="BN24" t="n">
+        <v>19</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS24" t="n">
         <v>801</v>
       </c>
     </row>
@@ -14860,7 +15482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS23"/>
+  <dimension ref="A1:BS24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22060,6 +22682,317 @@
       </c>
       <c r="BS23" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09:18:51</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>00:57</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>21:22</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>01:32</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>05:42</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>22:57</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>73</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>03:35</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>22:56</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>71</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>02:22</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>04:28</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AZ24" t="n">
+        <v>70</v>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC24" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>57</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>347</v>
+      </c>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN24" t="n">
+        <v>44</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS24" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -22073,7 +23006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS23"/>
+  <dimension ref="A1:BS24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29272,6 +30205,317 @@
         </is>
       </c>
       <c r="BS23" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09:18:51</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>00:52</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>21:11</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>01:28</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>05:45</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>21:56</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>22:48</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>03:35</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>22:48</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>02:19</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>04:29</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AZ24" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC24" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>53</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ24" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>120</v>
+      </c>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="BN24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS24" t="n">
         <v>800</v>
       </c>
     </row>
@@ -29286,7 +30530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS23"/>
+  <dimension ref="A1:BS24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36434,6 +37678,317 @@
       </c>
       <c r="BS23" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09:18:51</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>00:47</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>06:35</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>01:23</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>05:40</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>06:48</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>22:44</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>22:44</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>02:14</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>54</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>04:24</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="AZ24" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC24" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>51</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>50</v>
+      </c>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN24" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1019</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS24" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -36447,7 +38002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS23"/>
+  <dimension ref="A1:BS24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43646,6 +45201,317 @@
         </is>
       </c>
       <c r="BS23" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09:18:52</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>01:02</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>06:49</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>21:27</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>01:37</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>05:47</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>23:03</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>03:40</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>23:01</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>71</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>02:27</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>04:33</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AZ24" t="n">
+        <v>70</v>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC24" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>71</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>350</v>
+      </c>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN24" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS24" t="n">
         <v>800</v>
       </c>
     </row>
@@ -43660,7 +45526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS23"/>
+  <dimension ref="A1:BS24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50860,6 +52726,317 @@
       </c>
       <c r="BS23" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09:18:52</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>00:56</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>01:31</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>05:43</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>03:35</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>22:54</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>02:21</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>53</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>04:28</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AZ24" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC24" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>339</v>
+      </c>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN24" t="n">
+        <v>30</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS24" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -50873,7 +53050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS23"/>
+  <dimension ref="A1:BS24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58035,6 +60212,317 @@
       </c>
       <c r="BS23" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09:18:52</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>00:13</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>00:49</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>05:02</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>21:20</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>02:54</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>66</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>01:39</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>03:47</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AZ24" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC24" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>58</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>300</v>
+      </c>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>KBB</t>
+        </is>
+      </c>
+      <c r="BN24" t="n">
+        <v>26</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS24" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -58048,7 +60536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS23"/>
+  <dimension ref="A1:BS24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65200,6 +67688,317 @@
       </c>
       <c r="BS23" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09:18:52</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>00:07</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>05:56</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>00:45</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>05:07</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>06:14</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>21:09</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>02:55</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>68</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>01:36</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>03:49</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AZ24" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC24" t="n">
+        <v>18.58</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>18.58</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>18.58</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>35</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>149</v>
+      </c>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>GGD</t>
+        </is>
+      </c>
+      <c r="BN24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS24" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -65213,7 +68012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS23"/>
+  <dimension ref="A1:BS24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72412,6 +75211,317 @@
         </is>
       </c>
       <c r="BS23" t="n">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09:18:52</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>01:21</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>07:09</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>21:42</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>01:56</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>22:26</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>23:19</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>04:02</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>23:18</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>02:47</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>04:55</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
+      <c r="AZ24" t="n">
+        <v>71</v>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC24" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>27</v>
+      </c>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN24" t="n">
+        <v>35</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS24" t="n">
         <v>802</v>
       </c>
     </row>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS24"/>
+  <dimension ref="A1:BS25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7944,6 +7944,317 @@
         </is>
       </c>
       <c r="BS24" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>08:07:32</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>71</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>01:09</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>07:17</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>20:57</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>01:18</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>05:39</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>21:48</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>22:39</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>03:29</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>68</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>22:36</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>02:09</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>04:21</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AZ25" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC25" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>51</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>357</v>
+      </c>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS25" t="n">
         <v>800</v>
       </c>
     </row>
@@ -7958,7 +8269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS24"/>
+  <dimension ref="A1:BS25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15469,6 +15780,317 @@
       </c>
       <c r="BS24" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>08:07:33</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>01:18</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>21:14</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>01:27</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>05:39</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>22:03</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>22:54</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>03:34</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>66</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>22:50</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>02:17</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>04:25</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="AZ25" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC25" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>66</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>318</v>
+      </c>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1019</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS25" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -15482,7 +16104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS24"/>
+  <dimension ref="A1:BS25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22993,6 +23615,317 @@
       </c>
       <c r="BS24" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>08:07:32</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>01:19</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>01:28</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>05:38</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>22:07</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>22:58</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>03:34</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>71</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>02:18</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>04:24</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="AZ25" t="n">
+        <v>70</v>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC25" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>58</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>351</v>
+      </c>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS25" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -23006,7 +23939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS24"/>
+  <dimension ref="A1:BS25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30516,6 +31449,317 @@
         </is>
       </c>
       <c r="BS24" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>08:07:32</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>01:15</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>01:24</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>05:41</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>21:57</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>22:48</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>03:33</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>22:44</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>04:25</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AZ25" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC25" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>49</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ25" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>34</v>
+      </c>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS25" t="n">
         <v>800</v>
       </c>
     </row>
@@ -30530,7 +31774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS24"/>
+  <dimension ref="A1:BS25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37988,6 +39232,317 @@
         </is>
       </c>
       <c r="BS24" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>08:07:33</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>01:10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>01:19</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>21:53</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>76</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>22:44</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>54</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AZ25" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC25" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>54</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>43</v>
+      </c>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN25" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS25" t="n">
         <v>800</v>
       </c>
     </row>
@@ -38002,7 +39557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS24"/>
+  <dimension ref="A1:BS25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45512,6 +47067,317 @@
         </is>
       </c>
       <c r="BS24" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>08:07:33</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>01:24</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>21:23</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>01:33</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>05:43</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>06:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>23:03</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>03:39</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>22:58</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>02:23</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>04:29</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AZ25" t="n">
+        <v>70</v>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC25" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN25" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS25" t="n">
         <v>800</v>
       </c>
     </row>
@@ -45526,7 +47392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS24"/>
+  <dimension ref="A1:BS25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53037,6 +54903,317 @@
       </c>
       <c r="BS24" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>08:07:33</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>01:18</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>21:14</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>01:27</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>05:39</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>22:04</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>03:33</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>22:50</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>02:17</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>53</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>04:24</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AZ25" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC25" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>23</v>
+      </c>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS25" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -53050,7 +55227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS24"/>
+  <dimension ref="A1:BS25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60523,6 +62700,317 @@
       </c>
       <c r="BS24" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>08:07:33</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>00:35</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>00:45</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>04:59</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>06:14</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>02:53</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>01:36</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>03:44</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AZ25" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC25" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ25" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>11</v>
+      </c>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN25" t="n">
+        <v>77</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS25" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -60536,7 +63024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS24"/>
+  <dimension ref="A1:BS25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67998,6 +70486,317 @@
         </is>
       </c>
       <c r="BS24" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>08:07:33</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>00:31</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>20:19</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>00:41</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>05:03</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>06:17</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>02:53</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>01:32</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AZ25" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC25" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>52</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ25" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>107</v>
+      </c>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="BN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS25" t="n">
         <v>800</v>
       </c>
     </row>
@@ -68012,7 +70811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS24"/>
+  <dimension ref="A1:BS25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75523,6 +78322,317 @@
       </c>
       <c r="BS24" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>08:07:33</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dolunay</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>01:44</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>21:38</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>01:52</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>22:28</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>23:19</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>72</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>02:43</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>04:51</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="AZ25" t="n">
+        <v>71</v>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC25" t="n">
+        <v>24.36</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>24.31</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>24.36</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>24.36</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>56</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>15</v>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ25" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>43</v>
+      </c>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS25" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS25"/>
+  <dimension ref="A1:BS26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8255,6 +8255,317 @@
         </is>
       </c>
       <c r="BS25" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>10:42:46</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>01:33</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>01:14</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>05:35</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>21:48</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>03:27</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>22:32</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>02:05</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>04:17</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AZ26" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC26" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>41</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ26" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>353</v>
+      </c>
+      <c r="BM26" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS26" t="n">
         <v>800</v>
       </c>
     </row>
@@ -8269,7 +8580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS25"/>
+  <dimension ref="A1:BS26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16091,6 +16402,317 @@
       </c>
       <c r="BS25" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>10:42:47</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>01:41</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>01:23</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>05:35</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>06:58</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>22:04</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>03:32</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>22:47</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>02:13</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>04:21</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AZ26" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC26" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>47</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>331</v>
+      </c>
+      <c r="BM26" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN26" t="n">
+        <v>98</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS26" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -16104,7 +16726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS25"/>
+  <dimension ref="A1:BS26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23926,6 +24548,317 @@
       </c>
       <c r="BS25" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>10:42:46</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>33</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>01:41</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>21:14</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>01:24</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>05:34</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>06:57</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>22:07</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>22:58</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>03:32</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>22:50</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>02:14</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AZ26" t="n">
+        <v>70</v>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC26" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>53</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>185</v>
+      </c>
+      <c r="BM26" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BN26" t="n">
+        <v>98</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS26" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -23939,7 +24872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS25"/>
+  <dimension ref="A1:BS26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31760,6 +32693,317 @@
         </is>
       </c>
       <c r="BS25" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>10:42:46</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>01:39</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>01:20</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>05:37</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>06:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>76</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>22:49</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>03:32</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>04:21</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AZ26" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC26" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ26" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>55</v>
+      </c>
+      <c r="BM26" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR26" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS26" t="n">
         <v>800</v>
       </c>
     </row>
@@ -31774,7 +33018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS25"/>
+  <dimension ref="A1:BS26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39544,6 +40788,317 @@
       </c>
       <c r="BS25" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>10:42:46</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>01:34</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>01:15</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>05:32</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>03:27</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>22:37</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>02:07</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>04:16</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AZ26" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC26" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ26" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>47</v>
+      </c>
+      <c r="BM26" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN26" t="n">
+        <v>19</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS26" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -39557,7 +41112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS25"/>
+  <dimension ref="A1:BS26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47379,6 +48934,317 @@
       </c>
       <c r="BS25" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>10:42:46</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>01:46</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>21:19</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>01:29</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>05:39</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>22:13</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>23:03</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>03:37</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>02:19</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>04:25</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AZ26" t="n">
+        <v>70</v>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC26" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>53</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>310</v>
+      </c>
+      <c r="BM26" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS26" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -47392,7 +49258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS25"/>
+  <dimension ref="A1:BS26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55214,6 +57080,317 @@
       </c>
       <c r="BS25" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>10:42:47</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>01:41</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>01:23</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>05:35</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>06:57</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>03:32</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>22:47</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>02:13</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>53</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AZ26" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC26" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>22.84</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BM26" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="BN26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR26" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS26" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -55227,7 +57404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS25"/>
+  <dimension ref="A1:BS26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63010,6 +65187,317 @@
         </is>
       </c>
       <c r="BS25" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>10:42:47</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>00:59</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>00:41</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>04:55</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>06:17</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>21:22</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>02:51</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>01:32</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>03:40</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AZ26" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC26" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>266</v>
+      </c>
+      <c r="BM26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN26" t="n">
+        <v>54</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR26" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS26" t="n">
         <v>803</v>
       </c>
     </row>
@@ -63024,7 +65512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS25"/>
+  <dimension ref="A1:BS26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70797,6 +73285,317 @@
         </is>
       </c>
       <c r="BS25" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>10:42:47</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>00:56</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>00:37</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>04:59</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>21:11</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>02:51</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>07:27</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>21:55</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>01:29</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>03:41</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AZ26" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC26" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>31</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>207</v>
+      </c>
+      <c r="BM26" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN26" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR26" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS26" t="n">
         <v>800</v>
       </c>
     </row>
@@ -70811,7 +73610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS25"/>
+  <dimension ref="A1:BS26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78633,6 +81432,317 @@
       </c>
       <c r="BS25" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>10:42:47</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>02:07</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>01:48</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>06:03</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>22:29</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>23:19</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>03:58</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>23:11</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>02:39</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>04:47</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AZ26" t="n">
+        <v>71</v>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC26" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>54</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ26" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>45</v>
+      </c>
+      <c r="BM26" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR26" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS26" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS26"/>
+  <dimension ref="A1:BS27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8567,6 +8567,317 @@
       </c>
       <c r="BS26" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>08:17:33</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>55</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>01:10</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>05:31</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>06:58</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>21:49</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>03:25</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>22:29</t>
+        </is>
+      </c>
+      <c r="AN27" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>02:02</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>04:14</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AZ27" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC27" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>226</v>
+      </c>
+      <c r="BM27" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="BN27" t="n">
+        <v>50</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR27" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS27" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -8580,7 +8891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS26"/>
+  <dimension ref="A1:BS27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16712,6 +17023,317 @@
         </is>
       </c>
       <c r="BS26" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>08:17:35</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>02:06</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>21:06</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>01:19</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>05:31</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>73</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="AN27" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>04:17</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AZ27" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC27" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>83</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>Yuksek</t>
+        </is>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>314</v>
+      </c>
+      <c r="BM27" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN27" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>4929</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS27" t="n">
         <v>804</v>
       </c>
     </row>
@@ -16726,7 +17348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS26"/>
+  <dimension ref="A1:BS27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24858,6 +25480,317 @@
         </is>
       </c>
       <c r="BS26" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>08:17:34</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>02:06</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>01:20</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>06:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>74</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>22:58</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>22:47</t>
+        </is>
+      </c>
+      <c r="AN27" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>04:16</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AZ27" t="n">
+        <v>70</v>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC27" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>80</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>244</v>
+      </c>
+      <c r="BM27" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN27" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>9301</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS27" t="n">
         <v>804</v>
       </c>
     </row>
@@ -24872,7 +25805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS26"/>
+  <dimension ref="A1:BS27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33005,6 +33938,317 @@
       </c>
       <c r="BS26" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>08:17:34</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>02:05</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>01:16</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>05:33</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>22:49</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>22:38</t>
+        </is>
+      </c>
+      <c r="AN27" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>02:08</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>04:18</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AZ27" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC27" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>56</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ27" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>343</v>
+      </c>
+      <c r="BM27" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN27" t="n">
+        <v>68</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR27" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS27" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -33018,7 +34262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS26"/>
+  <dimension ref="A1:BS27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41099,6 +42343,317 @@
       </c>
       <c r="BS26" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>08:17:34</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>01:12</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>05:28</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>03:25</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>22:34</t>
+        </is>
+      </c>
+      <c r="AN27" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>02:03</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>04:12</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AZ27" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC27" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>63</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ27" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>50</v>
+      </c>
+      <c r="BM27" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN27" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS27" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -41112,7 +42667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS26"/>
+  <dimension ref="A1:BS27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49244,6 +50799,317 @@
         </is>
       </c>
       <c r="BS26" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>08:17:34</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>34</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>01:25</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>05:35</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>07:04</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>22:13</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>74</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>23:03</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>03:35</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>22:52</t>
+        </is>
+      </c>
+      <c r="AN27" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>02:16</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>04:21</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AZ27" t="n">
+        <v>70</v>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC27" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>85</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>Yuksek</t>
+        </is>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>108</v>
+      </c>
+      <c r="BM27" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="BN27" t="n">
+        <v>88</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS27" t="n">
         <v>804</v>
       </c>
     </row>
@@ -49258,7 +51124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS26"/>
+  <dimension ref="A1:BS27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57390,6 +59256,317 @@
         </is>
       </c>
       <c r="BS26" t="n">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>08:17:34</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>02:06</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>01:19</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>05:31</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>22:44</t>
+        </is>
+      </c>
+      <c r="AN27" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>53</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>04:17</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AZ27" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC27" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>85</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>14</v>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>Yuksek</t>
+        </is>
+      </c>
+      <c r="BJ27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>249</v>
+      </c>
+      <c r="BM27" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN27" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS27" t="n">
         <v>804</v>
       </c>
     </row>
@@ -57404,7 +59581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS26"/>
+  <dimension ref="A1:BS27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65499,6 +67676,317 @@
       </c>
       <c r="BS26" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>08:17:34</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>72</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>01:24</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>00:37</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>04:51</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>06:19</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>21:22</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>22:13</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>02:49</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="AN27" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>01:28</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>03:36</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AZ27" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC27" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>58</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>202</v>
+      </c>
+      <c r="BM27" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN27" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS27" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -65512,7 +68000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS26"/>
+  <dimension ref="A1:BS27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73596,6 +76084,317 @@
         </is>
       </c>
       <c r="BS26" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>08:17:35</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>01:23</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>00:33</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>04:55</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>21:12</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>02:49</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="AN27" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>01:25</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>03:38</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AZ27" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC27" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>41</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>184</v>
+      </c>
+      <c r="BM27" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BN27" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS27" t="n">
         <v>800</v>
       </c>
     </row>
@@ -73610,7 +76409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS26"/>
+  <dimension ref="A1:BS27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81743,6 +84542,317 @@
       </c>
       <c r="BS26" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>08:17:35</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>02:33</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>01:44</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>05:59</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>07:27</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>22:29</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>75</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>23:19</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>03:57</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>23:08</t>
+        </is>
+      </c>
+      <c r="AN27" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>04:44</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="AZ27" t="n">
+        <v>71</v>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC27" t="n">
+        <v>21.03</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>21.09</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>21.03</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>21.03</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>73</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>16</v>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>35</v>
+      </c>
+      <c r="BM27" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR27" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS27" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS27"/>
+  <dimension ref="A1:BS28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8878,6 +8878,317 @@
       </c>
       <c r="BS27" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>17:57:33</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>27</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>01:10</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>05:31</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>06:58</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>21:49</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>03:25</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>22:29</t>
+        </is>
+      </c>
+      <c r="AN28" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>02:02</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>04:14</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AZ28" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC28" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>128</v>
+      </c>
+      <c r="BM28" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="BN28" t="n">
+        <v>98</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR28" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS28" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -8891,7 +9202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS27"/>
+  <dimension ref="A1:BS28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17335,6 +17646,317 @@
       </c>
       <c r="BS27" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>17:57:36</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>27</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>02:06</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>21:06</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>01:19</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>05:31</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="AN28" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>04:17</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AZ28" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC28" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ28" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>338</v>
+      </c>
+      <c r="BM28" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN28" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR28" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS28" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -17348,7 +17970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS27"/>
+  <dimension ref="A1:BS28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25792,6 +26414,317 @@
       </c>
       <c r="BS27" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>17:57:33</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>63</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>27</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>02:06</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>01:20</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>06:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>22:58</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>66</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>22:47</t>
+        </is>
+      </c>
+      <c r="AN28" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>04:16</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AZ28" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC28" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>60</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ28" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>351</v>
+      </c>
+      <c r="BM28" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN28" t="n">
+        <v>13</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR28" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS28" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -25805,7 +26738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS27"/>
+  <dimension ref="A1:BS28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34249,6 +35182,317 @@
       </c>
       <c r="BS27" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>17:57:34</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>27</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>02:05</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>01:16</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>05:33</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>22:49</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>22:38</t>
+        </is>
+      </c>
+      <c r="AN28" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>02:08</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>04:18</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AZ28" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC28" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>37</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ28" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>306</v>
+      </c>
+      <c r="BM28" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN28" t="n">
+        <v>19</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1009</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="BR28" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS28" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -34262,7 +35506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS27"/>
+  <dimension ref="A1:BS28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42654,6 +43898,317 @@
       </c>
       <c r="BS27" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>17:57:34</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>27</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>01:12</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>05:28</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>03:25</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>22:34</t>
+        </is>
+      </c>
+      <c r="AN28" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>02:03</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>04:12</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AZ28" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC28" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>22.79</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>41</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ28" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>23</v>
+      </c>
+      <c r="BM28" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1010</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="BR28" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS28" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -42667,7 +44222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS27"/>
+  <dimension ref="A1:BS28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51111,6 +52666,317 @@
       </c>
       <c r="BS27" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>17:57:34</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>27</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>01:25</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>05:35</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>07:04</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>22:13</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>23:03</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>03:35</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>66</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>22:52</t>
+        </is>
+      </c>
+      <c r="AN28" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>02:16</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>04:21</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AZ28" t="n">
+        <v>70</v>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC28" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>20.57</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>61</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>13</v>
+      </c>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ28" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM28" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN28" t="n">
+        <v>43</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR28" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS28" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -51124,7 +52990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS27"/>
+  <dimension ref="A1:BS28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59568,6 +61434,317 @@
       </c>
       <c r="BS27" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>17:57:34</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>27</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>02:06</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>01:19</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>05:31</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>22:44</t>
+        </is>
+      </c>
+      <c r="AN28" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>04:17</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AZ28" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC28" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>54</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ28" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>123</v>
+      </c>
+      <c r="BM28" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="BN28" t="n">
+        <v>22</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR28" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS28" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -59581,7 +61758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS27"/>
+  <dimension ref="A1:BS28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67987,6 +70164,317 @@
       </c>
       <c r="BS27" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>17:57:34</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>67</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>27</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>01:24</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>00:37</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>04:51</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>06:19</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>21:22</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>22:13</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>02:49</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="AN28" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>01:28</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>03:36</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AZ28" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC28" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>21.03</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>53</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ28" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>269</v>
+      </c>
+      <c r="BM28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN28" t="n">
+        <v>13</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1011</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BR28" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS28" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -68000,7 +70488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS27"/>
+  <dimension ref="A1:BS28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76396,6 +78884,317 @@
       </c>
       <c r="BS27" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>17:57:35</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>27</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>01:23</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>00:33</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>04:55</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>21:12</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>02:49</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="AN28" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>01:25</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>03:38</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AZ28" t="n">
+        <v>73</v>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC28" t="n">
+        <v>21.38</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>21.38</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>21.38</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>47</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ28" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>193</v>
+      </c>
+      <c r="BM28" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN28" t="n">
+        <v>82</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR28" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS28" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -76409,7 +79208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS27"/>
+  <dimension ref="A1:BS28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84853,6 +87652,317 @@
       </c>
       <c r="BS27" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>17:57:36</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>27</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ilk Dordun</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>02:33</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>01:44</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>05:59</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>07:27</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>22:29</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>23:19</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>03:57</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>67</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>23:08</t>
+        </is>
+      </c>
+      <c r="AN28" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>04:44</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="AZ28" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC28" t="n">
+        <v>30.47</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>30.47</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>30.47</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>43</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ28" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>20</v>
+      </c>
+      <c r="BM28" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN28" t="n">
+        <v>36</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR28" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS28" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS28"/>
+  <dimension ref="A1:BS29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9189,6 +9189,317 @@
       </c>
       <c r="BS28" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>08:29:51</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>22:36</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>00:42</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>05:03</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>07:09</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>22:39</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>03:13</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>22:07</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>01:35</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>03:47</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AZ29" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC29" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>47</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>35</v>
+      </c>
+      <c r="BM29" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR29" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS29" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -9202,7 +9513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS28"/>
+  <dimension ref="A1:BS29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17956,6 +18267,317 @@
         </is>
       </c>
       <c r="BS28" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>08:29:53</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>22:50</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>20:38</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>00:51</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>05:04</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>22:54</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>03:17</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>01:43</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>03:51</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AZ29" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC29" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>58</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>276</v>
+      </c>
+      <c r="BM29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR29" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS29" t="n">
         <v>800</v>
       </c>
     </row>
@@ -17970,7 +18592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS28"/>
+  <dimension ref="A1:BS29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26725,6 +27347,317 @@
       </c>
       <c r="BS28" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>08:29:51</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>20:42</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>00:52</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>05:02</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>22:03</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>22:57</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>03:17</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>22:24</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>01:44</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>03:50</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AZ29" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC29" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>53</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>20</v>
+      </c>
+      <c r="BM29" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN29" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1019</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR29" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS29" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -26738,7 +27671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS28"/>
+  <dimension ref="A1:BS29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35493,6 +36426,317 @@
       </c>
       <c r="BS28" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>08:29:52</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>00:49</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>05:06</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>22:48</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>03:17</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>69</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>01:41</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>03:51</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AZ29" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC29" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>41</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ29" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>65</v>
+      </c>
+      <c r="BM29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1017</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR29" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS29" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -35506,7 +36750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS28"/>
+  <dimension ref="A1:BS29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44208,6 +45452,317 @@
         </is>
       </c>
       <c r="BS28" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>08:29:52</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>00:44</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>07:07</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>21:50</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>22:44</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>03:12</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>07:38</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>01:37</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>03:46</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AZ29" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC29" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>49</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ29" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>53</v>
+      </c>
+      <c r="BM29" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1020</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR29" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS29" t="n">
         <v>800</v>
       </c>
     </row>
@@ -44222,7 +45777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS28"/>
+  <dimension ref="A1:BS29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52977,6 +54532,317 @@
       </c>
       <c r="BS28" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>08:29:52</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>22:59</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>00:57</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>05:07</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>07:16</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>72</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>23:02</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>03:22</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>22:29</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>01:49</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>03:55</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="AZ29" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC29" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>67</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>53</v>
+      </c>
+      <c r="BM29" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN29" t="n">
+        <v>12</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1019</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR29" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS29" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -52990,7 +54856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS28"/>
+  <dimension ref="A1:BS29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61745,6 +63611,317 @@
       </c>
       <c r="BS28" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>08:29:52</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>22:51</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>20:39</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>00:51</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>05:03</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>22:54</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>03:17</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>01:43</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>03:51</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AZ29" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC29" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>49</v>
+      </c>
+      <c r="BM29" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN29" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR29" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS29" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -61758,7 +63935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS28"/>
+  <dimension ref="A1:BS29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70475,6 +72652,317 @@
       </c>
       <c r="BS28" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>08:29:52</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>22:07</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>00:10</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>04:23</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>21:17</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>07:38</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>21:39</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>01:02</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>07:14</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>03:10</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AZ29" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC29" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>53</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ29" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>97</v>
+      </c>
+      <c r="BM29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR29" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS29" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -70488,7 +72976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS28"/>
+  <dimension ref="A1:BS29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79195,6 +81683,317 @@
       </c>
       <c r="BS28" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>08:29:52</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>21:57</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>00:06</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>04:27</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>75</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>07:03</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>00:59</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>03:11</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AZ29" t="n">
+        <v>73</v>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC29" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>56</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>58</v>
+      </c>
+      <c r="BM29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BN29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1018</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR29" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS29" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -79208,7 +82007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS28"/>
+  <dimension ref="A1:BS29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87962,6 +90761,317 @@
         </is>
       </c>
       <c r="BS28" t="n">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>08:29:52</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>23:16</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>01:17</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>05:31</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>22:24</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>23:19</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>03:44</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>22:46</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>02:09</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>04:18</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AZ29" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC29" t="n">
+        <v>24.36</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>24.36</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>24.36</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>66</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ29" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>55</v>
+      </c>
+      <c r="BM29" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN29" t="n">
+        <v>25</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR29" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS29" t="n">
         <v>802</v>
       </c>
     </row>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS29"/>
+  <dimension ref="A1:BS30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9499,6 +9499,317 @@
         </is>
       </c>
       <c r="BS29" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>08:09:40</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>23:11</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>00:38</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>04:59</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>07:09</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>21:43</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>22:39</t>
+        </is>
+      </c>
+      <c r="AB30" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>03:11</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AH30" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>22:03</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>01:32</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>03:44</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AZ30" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC30" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>41</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>52</v>
+      </c>
+      <c r="BM30" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR30" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS30" t="n">
         <v>800</v>
       </c>
     </row>
@@ -9513,7 +9824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS29"/>
+  <dimension ref="A1:BS30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18579,6 +18890,317 @@
       </c>
       <c r="BS29" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>08:09:42</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>23:24</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>00:47</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="AB30" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>03:16</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AH30" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>22:18</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>03:47</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AZ30" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC30" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>60</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ30" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>47</v>
+      </c>
+      <c r="BM30" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN30" t="n">
+        <v>77</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR30" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS30" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -18592,7 +19214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS29"/>
+  <dimension ref="A1:BS30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27658,6 +28280,317 @@
       </c>
       <c r="BS29" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>08:09:40</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>23:26</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>20:38</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>00:48</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>04:58</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>22:56</t>
+        </is>
+      </c>
+      <c r="AB30" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>03:15</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AH30" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>03:47</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AZ30" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC30" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>64</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ30" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>357</v>
+      </c>
+      <c r="BM30" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN30" t="n">
+        <v>48</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR30" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS30" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -27671,7 +28604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS29"/>
+  <dimension ref="A1:BS30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36737,6 +37670,317 @@
       </c>
       <c r="BS29" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>08:09:41</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>23:19</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>00:45</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>05:02</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>07:13</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>22:48</t>
+        </is>
+      </c>
+      <c r="AB30" t="n">
+        <v>72</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>03:16</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AH30" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>01:38</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>03:48</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AZ30" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC30" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>43</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ30" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>50</v>
+      </c>
+      <c r="BM30" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN30" t="n">
+        <v>18</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR30" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS30" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -36750,7 +37994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS29"/>
+  <dimension ref="A1:BS30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45763,6 +47007,317 @@
         </is>
       </c>
       <c r="BS29" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>08:09:41</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>00:40</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>04:57</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>07:08</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>21:48</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>22:44</t>
+        </is>
+      </c>
+      <c r="AB30" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>03:11</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AH30" t="n">
+        <v>69</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>01:33</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>03:42</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AZ30" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC30" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>49</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ30" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>49</v>
+      </c>
+      <c r="BM30" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR30" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS30" t="n">
         <v>800</v>
       </c>
     </row>
@@ -45777,7 +47332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS29"/>
+  <dimension ref="A1:BS30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54843,6 +56398,317 @@
       </c>
       <c r="BS29" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>08:09:41</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>23:32</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>20:44</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>00:53</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>05:03</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>07:17</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>23:02</t>
+        </is>
+      </c>
+      <c r="AB30" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>03:20</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AH30" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>22:26</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>03:51</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AZ30" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC30" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>82</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ30" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM30" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN30" t="n">
+        <v>68</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR30" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS30" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -54856,7 +56722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS29"/>
+  <dimension ref="A1:BS30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63922,6 +65788,317 @@
       </c>
       <c r="BS29" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>08:09:41</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>23:24</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>00:47</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>04:59</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>22:54</t>
+        </is>
+      </c>
+      <c r="AB30" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>03:15</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AH30" t="n">
+        <v>68</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>22:18</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>03:47</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AZ30" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC30" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>60</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ30" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>41</v>
+      </c>
+      <c r="BM30" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN30" t="n">
+        <v>78</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR30" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS30" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -63935,7 +66112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS29"/>
+  <dimension ref="A1:BS30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72963,6 +75140,317 @@
       </c>
       <c r="BS29" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>08:09:41</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>00:06</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>04:19</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>21:16</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
+      </c>
+      <c r="AB30" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AH30" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>06:59</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>00:58</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>03:06</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AZ30" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC30" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>101</v>
+      </c>
+      <c r="BM30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BN30" t="n">
+        <v>22</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR30" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS30" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -72976,7 +75464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS29"/>
+  <dimension ref="A1:BS30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81993,6 +84481,317 @@
         </is>
       </c>
       <c r="BS29" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>08:09:41</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>22:33</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>00:02</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>04:24</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>21:06</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="AB30" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AH30" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>00:55</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>07:07</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>03:08</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AZ30" t="n">
+        <v>73</v>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC30" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>56</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ30" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>39</v>
+      </c>
+      <c r="BM30" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR30" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS30" t="n">
         <v>800</v>
       </c>
     </row>
@@ -82007,7 +84806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS29"/>
+  <dimension ref="A1:BS30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91072,6 +93871,317 @@
         </is>
       </c>
       <c r="BS29" t="n">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>08:09:41</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>23:49</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>01:13</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>05:27</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>22:22</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>23:18</t>
+        </is>
+      </c>
+      <c r="AB30" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>03:42</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AH30" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>22:42</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>02:05</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>04:14</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AZ30" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC30" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>59</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>30</v>
+      </c>
+      <c r="BM30" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN30" t="n">
+        <v>45</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR30" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS30" t="n">
         <v>802</v>
       </c>
     </row>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS30"/>
+  <dimension ref="A1:BS31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9811,6 +9811,317 @@
       </c>
       <c r="BS30" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>16:31:59</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>62</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>23:11</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>00:38</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>04:59</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>07:09</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>21:43</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>22:39</t>
+        </is>
+      </c>
+      <c r="AB31" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>03:11</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AH31" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>22:03</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>01:32</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AT31" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>03:44</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AZ31" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC31" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>47</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ31" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>160</v>
+      </c>
+      <c r="BM31" t="inlineStr">
+        <is>
+          <t>GGD</t>
+        </is>
+      </c>
+      <c r="BN31" t="n">
+        <v>30</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1010</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="BR31" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS31" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -9824,7 +10135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS30"/>
+  <dimension ref="A1:BS31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19201,6 +19512,317 @@
       </c>
       <c r="BS30" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>16:32:01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>23:24</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>00:47</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="AB31" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>03:16</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AH31" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>22:18</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AT31" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>03:47</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AZ31" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC31" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>23.11</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>37</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ31" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>241</v>
+      </c>
+      <c r="BM31" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN31" t="n">
+        <v>47</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1009</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="BR31" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS31" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -19214,7 +19836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS30"/>
+  <dimension ref="A1:BS31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28591,6 +29213,317 @@
       </c>
       <c r="BS30" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>16:31:59</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>23:26</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>20:38</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>00:48</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>04:58</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>22:56</t>
+        </is>
+      </c>
+      <c r="AB31" t="n">
+        <v>70</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>03:15</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AH31" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AT31" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>03:47</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AZ31" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC31" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ31" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM31" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN31" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR31" t="inlineStr">
+        <is>
+          <t>Hafif yağmur</t>
+        </is>
+      </c>
+      <c r="BS31" t="n">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -28604,7 +29537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS30"/>
+  <dimension ref="A1:BS31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37981,6 +38914,317 @@
       </c>
       <c r="BS30" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>16:32:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>23:19</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>00:45</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>05:02</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>07:13</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>22:48</t>
+        </is>
+      </c>
+      <c r="AB31" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>03:16</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AH31" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>01:38</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AT31" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>03:48</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AZ31" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC31" t="n">
+        <v>28.32</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>28.32</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>28.32</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>33</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ31" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>50</v>
+      </c>
+      <c r="BM31" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN31" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1006</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="BR31" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS31" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -37994,7 +39238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS30"/>
+  <dimension ref="A1:BS31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47318,6 +48562,317 @@
         </is>
       </c>
       <c r="BS30" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>16:32:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>00:40</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>04:57</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>07:08</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>21:48</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>73</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>22:44</t>
+        </is>
+      </c>
+      <c r="AB31" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>03:11</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AH31" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>01:33</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AT31" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>03:42</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AZ31" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC31" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ31" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>30</v>
+      </c>
+      <c r="BM31" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN31" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1007</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>52.16</v>
+      </c>
+      <c r="BR31" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS31" t="n">
         <v>800</v>
       </c>
     </row>
@@ -47332,7 +48887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS30"/>
+  <dimension ref="A1:BS31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56708,6 +58263,317 @@
         </is>
       </c>
       <c r="BS30" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>16:32:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>23:32</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>20:44</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>00:53</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>05:03</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>07:17</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>23:02</t>
+        </is>
+      </c>
+      <c r="AB31" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>03:20</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AH31" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>22:26</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AT31" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>03:51</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AZ31" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC31" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>64</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ31" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>7</v>
+      </c>
+      <c r="BM31" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN31" t="n">
+        <v>54</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR31" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS31" t="n">
         <v>803</v>
       </c>
     </row>
@@ -56722,7 +58588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS30"/>
+  <dimension ref="A1:BS31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66098,6 +67964,317 @@
         </is>
       </c>
       <c r="BS30" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>16:32:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>43</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>23:24</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>00:47</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>04:59</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>22:54</t>
+        </is>
+      </c>
+      <c r="AB31" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>03:15</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AH31" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>22:18</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>71</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AT31" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>03:47</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AZ31" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC31" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ31" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>20</v>
+      </c>
+      <c r="BM31" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN31" t="n">
+        <v>59</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1010</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="BR31" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS31" t="n">
         <v>803</v>
       </c>
     </row>
@@ -66112,7 +68289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS30"/>
+  <dimension ref="A1:BS31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75451,6 +77628,317 @@
       </c>
       <c r="BS30" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>16:32:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>00:06</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>04:19</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>21:16</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
+      </c>
+      <c r="AB31" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AH31" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>06:59</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>00:58</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AT31" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>03:06</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AZ31" t="n">
+        <v>71</v>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC31" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>72</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ31" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>63</v>
+      </c>
+      <c r="BM31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BN31" t="n">
+        <v>86</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR31" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS31" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -75464,7 +77952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS30"/>
+  <dimension ref="A1:BS31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84793,6 +87281,317 @@
       </c>
       <c r="BS30" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>16:32:01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>22:33</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>00:02</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>04:24</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>21:06</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="AB31" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AH31" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>00:55</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>07:07</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AT31" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>03:08</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AZ31" t="n">
+        <v>73</v>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC31" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ31" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>180</v>
+      </c>
+      <c r="BM31" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BN31" t="n">
+        <v>39</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1010</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="BR31" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS31" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -84806,7 +87605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS30"/>
+  <dimension ref="A1:BS31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94183,6 +96982,317 @@
       </c>
       <c r="BS30" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>16:32:01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>23:49</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>01:13</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>05:27</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>22:22</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>23:18</t>
+        </is>
+      </c>
+      <c r="AB31" t="n">
+        <v>71</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>03:42</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AH31" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>22:42</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>02:05</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AT31" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>04:14</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AZ31" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC31" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>38</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ31" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>28</v>
+      </c>
+      <c r="BM31" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN31" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR31" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS31" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS31"/>
+  <dimension ref="A1:BS32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10122,6 +10122,317 @@
       </c>
       <c r="BS31" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>08:36:56</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>00:34</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>04:55</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>21:41</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>22:39</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>03:10</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AH32" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AN32" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>01:28</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>03:40</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AZ32" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC32" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>73</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>230</v>
+      </c>
+      <c r="BM32" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="BN32" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>1011</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BR32" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS32" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -10135,7 +10446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS31"/>
+  <dimension ref="A1:BS32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19823,6 +20134,317 @@
       </c>
       <c r="BS31" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>08:36:57</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Zor</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>23:51</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>00:43</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>04:56</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>07:13</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>21:55</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>03:14</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AH32" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>22:14</t>
+        </is>
+      </c>
+      <c r="AN32" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>01:36</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>03:43</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="AZ32" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC32" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>86</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>Yuksek</t>
+        </is>
+      </c>
+      <c r="BJ32" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>258</v>
+      </c>
+      <c r="BM32" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN32" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR32" t="inlineStr">
+        <is>
+          <t>Kapalı</t>
+        </is>
+      </c>
+      <c r="BS32" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -19836,7 +20458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS31"/>
+  <dimension ref="A1:BS32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29523,6 +30145,317 @@
         </is>
       </c>
       <c r="BS31" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>08:36:56</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>23:53</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>00:44</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>04:55</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>22:56</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
+        <v>70</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>03:14</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AH32" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>22:17</t>
+        </is>
+      </c>
+      <c r="AN32" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>01:37</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>03:43</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AZ32" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC32" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>82</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>12</v>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ32" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>356</v>
+      </c>
+      <c r="BM32" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN32" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR32" t="inlineStr">
+        <is>
+          <t>Hafif yağmur</t>
+        </is>
+      </c>
+      <c r="BS32" t="n">
         <v>500</v>
       </c>
     </row>
@@ -29537,7 +30470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS31"/>
+  <dimension ref="A1:BS32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39225,6 +40158,317 @@
       </c>
       <c r="BS31" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>08:36:56</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>49</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>23:47</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>00:41</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>04:58</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>07:13</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>21:50</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>22:48</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>03:14</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AH32" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>22:09</t>
+        </is>
+      </c>
+      <c r="AN32" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>01:34</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>03:44</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AZ32" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC32" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>65</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>11</v>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ32" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>28</v>
+      </c>
+      <c r="BM32" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN32" t="n">
+        <v>51</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR32" t="inlineStr">
+        <is>
+          <t>Parçalı bulutlu</t>
+        </is>
+      </c>
+      <c r="BS32" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -39238,7 +40482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS31"/>
+  <dimension ref="A1:BS32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48873,6 +50117,317 @@
         </is>
       </c>
       <c r="BS31" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>08:36:56</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>23:43</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>00:36</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>04:53</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>07:08</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>73</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>03:09</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AH32" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="AN32" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>01:29</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>03:39</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AZ32" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC32" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>71</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ32" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>19</v>
+      </c>
+      <c r="BM32" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN32" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR32" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS32" t="n">
         <v>800</v>
       </c>
     </row>
@@ -48887,7 +50442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS31"/>
+  <dimension ref="A1:BS32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58575,6 +60130,317 @@
       </c>
       <c r="BS31" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>08:36:57</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>23:59</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>00:49</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>04:59</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>07:17</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>22:04</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>23:01</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>03:18</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AH32" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>22:22</t>
+        </is>
+      </c>
+      <c r="AN32" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>01:42</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>03:48</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AZ32" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC32" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>81</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ32" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>352</v>
+      </c>
+      <c r="BM32" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN32" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>1016</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR32" t="inlineStr">
+        <is>
+          <t>Hafif yağmur</t>
+        </is>
+      </c>
+      <c r="BS32" t="n">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -58588,7 +60454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS31"/>
+  <dimension ref="A1:BS32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68276,6 +70142,317 @@
       </c>
       <c r="BS31" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>08:36:57</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Gozlem Yapilamaz</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>23:52</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>00:43</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>04:55</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>21:56</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>03:14</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AH32" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="AN32" t="n">
+        <v>71</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>01:36</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>03:43</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="AZ32" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC32" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>86</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>Yuksek</t>
+        </is>
+      </c>
+      <c r="BJ32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>32</v>
+      </c>
+      <c r="BM32" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN32" t="n">
+        <v>100</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR32" t="inlineStr">
+        <is>
+          <t>Hafif yağmur</t>
+        </is>
+      </c>
+      <c r="BS32" t="n">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -68289,7 +70466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS31"/>
+  <dimension ref="A1:BS32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77939,6 +80116,317 @@
       </c>
       <c r="BS31" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>08:36:57</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>23:09</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>00:02</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>02:33</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AH32" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>21:32</t>
+        </is>
+      </c>
+      <c r="AN32" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>00:54</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>07:07</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>03:02</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AZ32" t="n">
+        <v>71</v>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC32" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>43</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>184</v>
+      </c>
+      <c r="BM32" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="BN32" t="n">
+        <v>12</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR32" t="inlineStr">
+        <is>
+          <t>Az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS32" t="n">
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -77952,7 +80440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS31"/>
+  <dimension ref="A1:BS32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87592,6 +90080,317 @@
       </c>
       <c r="BS31" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>08:36:57</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>23:02</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>19:36</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>23:58</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>02:34</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AH32" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>06:58</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>21:23</t>
+        </is>
+      </c>
+      <c r="AN32" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>00:51</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>07:03</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>03:04</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AZ32" t="n">
+        <v>73</v>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC32" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>192</v>
+      </c>
+      <c r="BM32" t="inlineStr">
+        <is>
+          <t>GGB</t>
+        </is>
+      </c>
+      <c r="BN32" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR32" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS32" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -87605,7 +90404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS31"/>
+  <dimension ref="A1:BS32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97293,6 +100092,317 @@
       </c>
       <c r="BS31" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>08:36:57</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hilal</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Uygun</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>00:17</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>01:09</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>05:23</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>22:20</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>23:18</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
+        <v>71</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>03:40</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AH32" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>22:39</t>
+        </is>
+      </c>
+      <c r="AN32" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>02:02</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>04:10</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AZ32" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC32" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>21.41</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>62</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>14</v>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ32" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>34</v>
+      </c>
+      <c r="BM32" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN32" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR32" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS32" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS32"/>
+  <dimension ref="A1:BS33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10432,6 +10432,317 @@
         </is>
       </c>
       <c r="BS32" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10:29:44</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>01:16</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>00:19</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>04:40</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>07:07</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>22:37</t>
+        </is>
+      </c>
+      <c r="AB33" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>03:03</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AH33" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>21:47</t>
+        </is>
+      </c>
+      <c r="AN33" t="n">
+        <v>73</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>01:13</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>03:25</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AZ33" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC33" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>73</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>13</v>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="BJ33" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>282</v>
+      </c>
+      <c r="BM33" t="inlineStr">
+        <is>
+          <t>KBB</t>
+        </is>
+      </c>
+      <c r="BN33" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR33" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS33" t="n">
         <v>800</v>
       </c>
     </row>
@@ -10446,7 +10757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS32"/>
+  <dimension ref="A1:BS33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20445,6 +20756,317 @@
       </c>
       <c r="BS32" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10:29:46</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>01:22</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>00:28</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>04:40</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>21:44</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>22:51</t>
+        </is>
+      </c>
+      <c r="AB33" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>03:07</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AH33" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="AN33" t="n">
+        <v>71</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>01:21</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AZ33" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC33" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>307</v>
+      </c>
+      <c r="BM33" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>1011</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BR33" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS33" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -20458,7 +21080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS32"/>
+  <dimension ref="A1:BS33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30457,6 +31079,317 @@
       </c>
       <c r="BS32" t="n">
         <v>500</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10:29:44</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>01:22</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>20:19</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>00:29</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>04:39</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>21:47</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>22:54</t>
+        </is>
+      </c>
+      <c r="AB33" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>03:07</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AH33" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>22:04</t>
+        </is>
+      </c>
+      <c r="AN33" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>01:22</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AZ33" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC33" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>347</v>
+      </c>
+      <c r="BM33" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR33" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS33" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -30470,7 +31403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS32"/>
+  <dimension ref="A1:BS33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40469,6 +41402,317 @@
       </c>
       <c r="BS32" t="n">
         <v>803</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10:29:44</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>01:21</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>00:25</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>04:42</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>21:38</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>22:46</t>
+        </is>
+      </c>
+      <c r="AB33" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>03:07</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AH33" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>21:56</t>
+        </is>
+      </c>
+      <c r="AN33" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>01:19</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>03:29</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AZ33" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC33" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ33" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>358</v>
+      </c>
+      <c r="BM33" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR33" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS33" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -40482,7 +41726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS32"/>
+  <dimension ref="A1:BS33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50429,6 +51673,317 @@
       </c>
       <c r="BS32" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10:29:45</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>01:16</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>00:20</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>04:37</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="AB33" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>03:02</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AH33" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="AN33" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>01:14</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>07:27</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>03:24</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AZ33" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC33" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>64</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ33" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>13</v>
+      </c>
+      <c r="BM33" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN33" t="n">
+        <v>46</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR33" t="inlineStr">
+        <is>
+          <t>Parçalı az bulutlu</t>
+        </is>
+      </c>
+      <c r="BS33" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>
@@ -50442,7 +51997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS32"/>
+  <dimension ref="A1:BS33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60441,6 +61996,317 @@
       </c>
       <c r="BS32" t="n">
         <v>500</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10:29:45</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>74</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>01:27</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>00:34</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>04:44</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>22:59</t>
+        </is>
+      </c>
+      <c r="AB33" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>03:12</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AH33" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>22:10</t>
+        </is>
+      </c>
+      <c r="AN33" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>01:27</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>03:33</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AZ33" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC33" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>35</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>337</v>
+      </c>
+      <c r="BM33" t="inlineStr">
+        <is>
+          <t>KKB</t>
+        </is>
+      </c>
+      <c r="BN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR33" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS33" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -60454,7 +62320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS32"/>
+  <dimension ref="A1:BS33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70453,6 +72319,317 @@
       </c>
       <c r="BS32" t="n">
         <v>500</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10:29:45</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>01:22</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>00:28</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>04:40</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>21:44</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>22:51</t>
+        </is>
+      </c>
+      <c r="AB33" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>03:07</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AH33" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="AN33" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>01:21</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AZ33" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC33" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>49</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ33" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>27</v>
+      </c>
+      <c r="BM33" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>1011</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BR33" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS33" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -70466,7 +72643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS32"/>
+  <dimension ref="A1:BS33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80427,6 +82604,317 @@
       </c>
       <c r="BS32" t="n">
         <v>801</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10:29:45</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>00:40</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>23:46</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>21:02</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>71</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>22:09</t>
+        </is>
+      </c>
+      <c r="AB33" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>02:26</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AH33" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>21:19</t>
+        </is>
+      </c>
+      <c r="AN33" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>00:39</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>02:47</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AZ33" t="n">
+        <v>71</v>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC33" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>124</v>
+      </c>
+      <c r="BM33" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="BN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>1011</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BR33" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS33" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -80440,7 +82928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS32"/>
+  <dimension ref="A1:BS33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90390,6 +92878,317 @@
         </is>
       </c>
       <c r="BS32" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10:29:46</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Hakkâri</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>00:39</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>23:42</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>04:04</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>73</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AB33" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>02:27</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AH33" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>06:46</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="AN33" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>00:36</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>06:48</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>02:49</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AZ33" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC33" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>35</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ33" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>81</v>
+      </c>
+      <c r="BM33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR33" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS33" t="n">
         <v>800</v>
       </c>
     </row>
@@ -90404,7 +93203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS32"/>
+  <dimension ref="A1:BS33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100402,6 +103201,317 @@
         </is>
       </c>
       <c r="BS32" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10:29:46</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Assos</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>01:49</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>20:39</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>00:53</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>05:07</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>07:38</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>23:16</t>
+        </is>
+      </c>
+      <c r="AB33" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>03:34</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AH33" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>22:26</t>
+        </is>
+      </c>
+      <c r="AN33" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>01:47</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>03:55</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AZ33" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC33" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>53</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ33" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>36</v>
+      </c>
+      <c r="BM33" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR33" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS33" t="n">
         <v>800</v>
       </c>
     </row>

--- a/HavaTakip/astro_gozlem_verileri.xlsx
+++ b/HavaTakip/astro_gozlem_verileri.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS33"/>
+  <dimension ref="A1:BS34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10743,6 +10743,317 @@
         </is>
       </c>
       <c r="BS33" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>08:49:34</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Çamardı</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>01:43</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>19:54</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>00:15</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>04:36</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>22:37</t>
+        </is>
+      </c>
+      <c r="AB34" t="n">
+        <v>71</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>03:01</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AH34" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>21:44</t>
+        </is>
+      </c>
+      <c r="AN34" t="n">
+        <v>73</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>01:09</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AT34" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>03:21</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AZ34" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC34" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>64</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="BI34" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ34" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>323</v>
+      </c>
+      <c r="BM34" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="BN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR34" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS34" t="n">
         <v>800</v>
       </c>
     </row>
@@ -10757,7 +11068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS33"/>
+  <dimension ref="A1:BS34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21066,6 +21377,317 @@
         </is>
       </c>
       <c r="BS33" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>08:49:35</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Gölbaşı</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>20:44</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>01:47</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>00:24</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>04:36</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>22:50</t>
+        </is>
+      </c>
+      <c r="AB34" t="n">
+        <v>69</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>03:05</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AH34" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="AN34" t="n">
+        <v>71</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>01:17</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AT34" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>03:25</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AZ34" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC34" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>64</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="BI34" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>248</v>
+      </c>
+      <c r="BM34" t="inlineStr">
+        <is>
+          <t>BGB</t>
+        </is>
+      </c>
+      <c r="BN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR34" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS34" t="n">
         <v>800</v>
       </c>
     </row>
@@ -21080,7 +21702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS33"/>
+  <dimension ref="A1:BS34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31389,6 +32011,317 @@
         </is>
       </c>
       <c r="BS33" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>08:49:34</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Çamlıdere</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>01:47</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>00:25</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>04:35</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>07:09</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>21:43</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
+      </c>
+      <c r="AB34" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>03:05</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AH34" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="AN34" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>01:18</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AT34" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>03:24</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AZ34" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC34" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>52</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BI34" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>50</v>
+      </c>
+      <c r="BM34" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>1014</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR34" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS34" t="n">
         <v>800</v>
       </c>
     </row>
@@ -31403,7 +32336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS33"/>
+  <dimension ref="A1:BS34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41712,6 +42645,317 @@
         </is>
       </c>
       <c r="BS33" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>08:49:34</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Koçhisar</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>20:41</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>01:47</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>20:04</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>00:21</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>04:38</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="AB34" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>03:06</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AH34" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>07:23</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>21:53</t>
+        </is>
+      </c>
+      <c r="AN34" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>01:15</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>07:27</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AT34" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>03:25</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AZ34" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC34" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>52</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BI34" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ34" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>38</v>
+      </c>
+      <c r="BM34" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR34" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS34" t="n">
         <v>800</v>
       </c>
     </row>
@@ -41726,7 +42970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS33"/>
+  <dimension ref="A1:BS34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51984,6 +53228,317 @@
       </c>
       <c r="BS33" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>08:49:34</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Hacıbektaş</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>65</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>20:36</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>01:42</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>00:16</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>04:33</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="AB34" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AH34" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>21:49</t>
+        </is>
+      </c>
+      <c r="AN34" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>01:10</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>07:23</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AT34" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>03:20</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AZ34" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC34" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>61</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BI34" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ34" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>28</v>
+      </c>
+      <c r="BM34" t="inlineStr">
+        <is>
+          <t>KKD</t>
+        </is>
+      </c>
+      <c r="BN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR34" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS34" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -51997,7 +53552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS33"/>
+  <dimension ref="A1:BS34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62306,6 +63861,317 @@
         </is>
       </c>
       <c r="BS33" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>08:49:34</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Mudurnu</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>01:52</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>04:40</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>07:14</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>21:48</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>22:58</t>
+        </is>
+      </c>
+      <c r="AB34" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>03:10</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AH34" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>07:27</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="AN34" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>01:23</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AT34" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>03:29</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AZ34" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC34" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>56</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="BI34" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ34" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM34" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="BN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>1015</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR34" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS34" t="n">
         <v>800</v>
       </c>
     </row>
@@ -62320,7 +64186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS33"/>
+  <dimension ref="A1:BS34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72629,6 +74495,317 @@
         </is>
       </c>
       <c r="BS33" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>08:49:34</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Yenimahalle</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Ay Fotografciligi Uygun</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>20:44</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>01:47</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>00:24</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>04:36</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>07:09</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>22:51</t>
+        </is>
+      </c>
+      <c r="AB34" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>03:05</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AH34" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>21:59</t>
+        </is>
+      </c>
+      <c r="AN34" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>01:17</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AT34" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>03:24</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AZ34" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="BC34" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>56</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="BI34" t="inlineStr">
+        <is>
+          <t>Dusuk</t>
+        </is>
+      </c>
+      <c r="BJ34" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>55</v>
+      </c>
+      <c r="BM34" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="BN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>1012</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BR34" t="inlineStr">
+        <is>
+          <t>Açık</t>
+        </is>
+      </c>
+      <c r="BS34" t="n">
         <v>800</v>
       </c>
     </row>
@@ -72643,7 +74820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS33"/>
+  <dimension ref="A1:BS34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82915,6 +85092,317 @@
       </c>
       <c r="BS33" t="n">
         <v>800</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>08:49:34</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ağrı</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Son Dordun</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Orta</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>01:05</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>DGD</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>19:29</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>23:42</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>03:56</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Zirve</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>06:29</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>20:58</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="AB34" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>02:24</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AH34" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>21:16</t>
+        </is>
+      </c>
+      <c r="AN34" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>DKD</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>İyi</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>00:36</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>06:48</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AT34" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>D</t>
+